--- a/2026-09-28/Roster_Sep28_Oct11_Full.xlsx
+++ b/2026-09-28/Roster_Sep28_Oct11_Full.xlsx
@@ -10,6 +10,8 @@
     <sheet name="DBZ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="KM" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Mirkl" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="KM Shift Snapshot" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mirkl Shift Snapshot" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +43,17 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -97,8 +108,20 @@
         <bgColor rgb="0038761D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F6FC5"/>
+        <bgColor rgb="001F6FC5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E8449"/>
+        <bgColor rgb="001E8449"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -120,11 +143,55 @@
         <color rgb="00000000"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -158,6 +225,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -525,7 +603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q223"/>
+  <dimension ref="A1:Q222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -550,25 +628,25 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DBZ — Roster 28 Sep – 11 Oct 2026 (204 agents)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="2" t="n"/>
-      <c r="Q1" s="2" t="n"/>
+          <t>DBZ — Roster 28 Sep – 11 Oct 2026 (203 agents)</t>
+        </is>
+      </c>
+      <c r="B1" s="15" t="n"/>
+      <c r="C1" s="15" t="n"/>
+      <c r="D1" s="15" t="n"/>
+      <c r="E1" s="15" t="n"/>
+      <c r="F1" s="15" t="n"/>
+      <c r="G1" s="15" t="n"/>
+      <c r="H1" s="15" t="n"/>
+      <c r="I1" s="15" t="n"/>
+      <c r="J1" s="15" t="n"/>
+      <c r="K1" s="15" t="n"/>
+      <c r="L1" s="15" t="n"/>
+      <c r="M1" s="15" t="n"/>
+      <c r="N1" s="15" t="n"/>
+      <c r="O1" s="15" t="n"/>
+      <c r="P1" s="15" t="n"/>
+      <c r="Q1" s="16" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="n"/>
@@ -579,23 +657,23 @@
           <t>Week 1: 28 Sep – 4 Oct</t>
         </is>
       </c>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n"/>
-      <c r="I2" s="4" t="n"/>
-      <c r="J2" s="4" t="n"/>
+      <c r="E2" s="15" t="n"/>
+      <c r="F2" s="15" t="n"/>
+      <c r="G2" s="15" t="n"/>
+      <c r="H2" s="15" t="n"/>
+      <c r="I2" s="15" t="n"/>
+      <c r="J2" s="16" t="n"/>
       <c r="K2" s="5" t="inlineStr">
         <is>
           <t>Week 2: 5 Oct – 11 Oct</t>
         </is>
       </c>
-      <c r="L2" s="6" t="n"/>
-      <c r="M2" s="6" t="n"/>
-      <c r="N2" s="6" t="n"/>
-      <c r="O2" s="6" t="n"/>
-      <c r="P2" s="6" t="n"/>
-      <c r="Q2" s="6" t="n"/>
+      <c r="L2" s="15" t="n"/>
+      <c r="M2" s="15" t="n"/>
+      <c r="N2" s="15" t="n"/>
+      <c r="O2" s="15" t="n"/>
+      <c r="P2" s="15" t="n"/>
+      <c r="Q2" s="16" t="n"/>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
@@ -1325,27 +1403,27 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
@@ -1360,27 +1438,27 @@
       </c>
       <c r="K11" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="L11" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="M11" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="N11" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="O11" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="P11" s="10" t="inlineStr">
@@ -2301,12 +2379,12 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
@@ -2321,27 +2399,27 @@
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="J23" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="M23" s="10" t="inlineStr">
@@ -2356,17 +2434,17 @@
       </c>
       <c r="O23" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="P23" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="Q23" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
     </row>
@@ -5321,7 +5399,7 @@
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="F60" s="9" t="inlineStr">
@@ -5341,7 +5419,7 @@
       </c>
       <c r="I60" s="9" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="J60" s="10" t="inlineStr">
@@ -5356,7 +5434,7 @@
       </c>
       <c r="L60" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="M60" s="9" t="inlineStr">
@@ -5376,7 +5454,7 @@
       </c>
       <c r="P60" s="9" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="Q60" s="10" t="inlineStr">
@@ -6727,17 +6805,17 @@
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="E77" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="G77" s="9" t="inlineStr">
@@ -6752,7 +6830,7 @@
       </c>
       <c r="I77" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="J77" s="10" t="inlineStr">
@@ -6762,17 +6840,17 @@
       </c>
       <c r="K77" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="L77" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="M77" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="N77" s="9" t="inlineStr">
@@ -6787,7 +6865,7 @@
       </c>
       <c r="P77" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="Q77" s="10" t="inlineStr">
@@ -8858,17 +8936,17 @@
       </c>
       <c r="E103" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="G103" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="H103" s="10" t="inlineStr">
@@ -8903,17 +8981,17 @@
       </c>
       <c r="N103" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="O103" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="P103" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="Q103" s="9" t="inlineStr">
@@ -8955,22 +9033,22 @@
       </c>
       <c r="G104" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="H104" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="I104" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="J104" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="K104" s="9" t="inlineStr">
@@ -11592,7 +11670,7 @@
     <row r="137" ht="16" customHeight="1">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t>Darcy Ellison (DBZ)</t>
+          <t>Fen Lockhart (DBZ)</t>
         </is>
       </c>
       <c r="B137" s="8" t="inlineStr">
@@ -11605,34 +11683,34 @@
           <t>Robin Clarke</t>
         </is>
       </c>
-      <c r="D137" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="D137" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="E137" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="F137" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="G137" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="H137" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="I137" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="I137" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="J137" s="10" t="inlineStr">
@@ -11640,34 +11718,34 @@
           <t>WO</t>
         </is>
       </c>
-      <c r="K137" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="K137" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="L137" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="M137" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="N137" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="O137" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="P137" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="P137" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="Q137" s="10" t="inlineStr">
@@ -11679,7 +11757,7 @@
     <row r="138" ht="16" customHeight="1">
       <c r="A138" s="8" t="inlineStr">
         <is>
-          <t>Fen Lockhart (DBZ)</t>
+          <t>Nairn Bletchley (DBZ)</t>
         </is>
       </c>
       <c r="B138" s="8" t="inlineStr">
@@ -11692,9 +11770,9 @@
           <t>Robin Clarke</t>
         </is>
       </c>
-      <c r="D138" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="D138" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="E138" s="9" t="inlineStr">
@@ -11712,24 +11790,24 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="H138" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="I138" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="J138" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="K138" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="H138" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="I138" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="J138" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="K138" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="L138" s="9" t="inlineStr">
@@ -11747,26 +11825,26 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="O138" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="P138" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="Q138" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="O138" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="P138" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="Q138" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
         </is>
       </c>
     </row>
     <row r="139" ht="16" customHeight="1">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t>Nairn Bletchley (DBZ)</t>
+          <t>Orin Hartwell (DBZ)</t>
         </is>
       </c>
       <c r="B139" s="8" t="inlineStr">
@@ -11799,9 +11877,9 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="H139" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="H139" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="I139" s="10" t="inlineStr">
@@ -11809,9 +11887,9 @@
           <t>WO</t>
         </is>
       </c>
-      <c r="J139" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
+      <c r="J139" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="K139" s="9" t="inlineStr">
@@ -11834,9 +11912,9 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="O139" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="O139" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="P139" s="10" t="inlineStr">
@@ -11844,16 +11922,16 @@
           <t>WO</t>
         </is>
       </c>
-      <c r="Q139" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
+      <c r="Q139" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
     </row>
     <row r="140" ht="16" customHeight="1">
       <c r="A140" s="8" t="inlineStr">
         <is>
-          <t>Orin Hartwell (DBZ)</t>
+          <t>Piper Matthews (DBZ)</t>
         </is>
       </c>
       <c r="B140" s="8" t="inlineStr">
@@ -11866,9 +11944,9 @@
           <t>Robin Clarke</t>
         </is>
       </c>
-      <c r="D140" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
+      <c r="D140" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="E140" s="9" t="inlineStr">
@@ -11891,9 +11969,9 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="I140" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="I140" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="J140" s="10" t="inlineStr">
@@ -11901,9 +11979,9 @@
           <t>WO</t>
         </is>
       </c>
-      <c r="K140" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
+      <c r="K140" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="L140" s="9" t="inlineStr">
@@ -11926,9 +12004,9 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="P140" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="P140" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="Q140" s="10" t="inlineStr">
@@ -11940,7 +12018,7 @@
     <row r="141" ht="16" customHeight="1">
       <c r="A141" s="8" t="inlineStr">
         <is>
-          <t>Piper Matthews (DBZ)</t>
+          <t>Renley Cotsford (DBZ)</t>
         </is>
       </c>
       <c r="B141" s="8" t="inlineStr">
@@ -12027,7 +12105,7 @@
     <row r="142" ht="16" customHeight="1">
       <c r="A142" s="8" t="inlineStr">
         <is>
-          <t>Renley Cotsford (DBZ)</t>
+          <t>Sorrel Beckwith (DBZ)</t>
         </is>
       </c>
       <c r="B142" s="8" t="inlineStr">
@@ -12040,9 +12118,9 @@
           <t>Robin Clarke</t>
         </is>
       </c>
-      <c r="D142" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="D142" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="E142" s="9" t="inlineStr">
@@ -12050,14 +12128,14 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="F142" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="G142" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
+      <c r="F142" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="G142" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="H142" s="9" t="inlineStr">
@@ -12070,14 +12148,14 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="J142" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="K142" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="J142" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="K142" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="L142" s="9" t="inlineStr">
@@ -12085,14 +12163,14 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="M142" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="N142" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
+      <c r="M142" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="N142" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="O142" s="9" t="inlineStr">
@@ -12105,16 +12183,16 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="Q142" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="Q142" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
         </is>
       </c>
     </row>
     <row r="143" ht="16" customHeight="1">
       <c r="A143" s="8" t="inlineStr">
         <is>
-          <t>Sorrel Beckwith (DBZ)</t>
+          <t>Teagan Holbrook (DBZ)</t>
         </is>
       </c>
       <c r="B143" s="8" t="inlineStr">
@@ -12137,14 +12215,14 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="F143" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="G143" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="F143" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="G143" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="H143" s="9" t="inlineStr">
@@ -12152,14 +12230,14 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="I143" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="J143" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
+      <c r="I143" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="J143" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="K143" s="9" t="inlineStr">
@@ -12172,14 +12250,14 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="M143" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="N143" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="M143" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="N143" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="O143" s="9" t="inlineStr">
@@ -12187,21 +12265,21 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="P143" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="Q143" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
+      <c r="P143" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="Q143" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
     </row>
     <row r="144" ht="16" customHeight="1">
       <c r="A144" s="8" t="inlineStr">
         <is>
-          <t>Teagan Holbrook (DBZ)</t>
+          <t>Wynn Carleton (DBZ)</t>
         </is>
       </c>
       <c r="B144" s="8" t="inlineStr">
@@ -12219,14 +12297,14 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="E144" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="F144" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
+      <c r="E144" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="F144" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="G144" s="9" t="inlineStr">
@@ -12239,14 +12317,14 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="I144" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="J144" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="I144" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="J144" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="K144" s="9" t="inlineStr">
@@ -12254,14 +12332,14 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="L144" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="M144" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
+      <c r="L144" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="M144" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="N144" s="9" t="inlineStr">
@@ -12274,127 +12352,127 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="P144" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="Q144" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="P144" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="Q144" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
         </is>
       </c>
     </row>
     <row r="145" ht="16" customHeight="1">
-      <c r="A145" s="8" t="inlineStr">
-        <is>
-          <t>Wynn Carleton (DBZ)</t>
-        </is>
-      </c>
-      <c r="B145" s="8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C145" s="8" t="inlineStr">
-        <is>
-          <t>Robin Clarke</t>
-        </is>
-      </c>
-      <c r="D145" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="E145" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="F145" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="G145" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="H145" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="I145" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="J145" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="K145" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="L145" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="M145" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="N145" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="O145" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="P145" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="Q145" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
+      <c r="A145" s="11" t="n"/>
+      <c r="B145" s="11" t="n"/>
+      <c r="C145" s="11" t="n"/>
+      <c r="D145" s="11" t="n"/>
+      <c r="E145" s="11" t="n"/>
+      <c r="F145" s="11" t="n"/>
+      <c r="G145" s="11" t="n"/>
+      <c r="H145" s="11" t="n"/>
+      <c r="I145" s="11" t="n"/>
+      <c r="J145" s="11" t="n"/>
+      <c r="K145" s="11" t="n"/>
+      <c r="L145" s="11" t="n"/>
+      <c r="M145" s="11" t="n"/>
+      <c r="N145" s="11" t="n"/>
+      <c r="O145" s="11" t="n"/>
+      <c r="P145" s="11" t="n"/>
+      <c r="Q145" s="11" t="n"/>
     </row>
     <row r="146" ht="4" customHeight="1">
-      <c r="A146" s="11" t="n"/>
-      <c r="B146" s="11" t="n"/>
-      <c r="C146" s="11" t="n"/>
-      <c r="D146" s="11" t="n"/>
-      <c r="E146" s="11" t="n"/>
-      <c r="F146" s="11" t="n"/>
-      <c r="G146" s="11" t="n"/>
-      <c r="H146" s="11" t="n"/>
-      <c r="I146" s="11" t="n"/>
-      <c r="J146" s="11" t="n"/>
-      <c r="K146" s="11" t="n"/>
-      <c r="L146" s="11" t="n"/>
-      <c r="M146" s="11" t="n"/>
-      <c r="N146" s="11" t="n"/>
-      <c r="O146" s="11" t="n"/>
-      <c r="P146" s="11" t="n"/>
-      <c r="Q146" s="11" t="n"/>
+      <c r="A146" s="8" t="inlineStr">
+        <is>
+          <t>Addison Fairfax (DBZ)</t>
+        </is>
+      </c>
+      <c r="B146" s="8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C146" s="8" t="inlineStr">
+        <is>
+          <t>Rory Sanderson</t>
+        </is>
+      </c>
+      <c r="D146" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="E146" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="F146" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="G146" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="H146" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="I146" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="J146" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="K146" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="L146" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="M146" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="N146" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="O146" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="P146" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="Q146" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="16" customHeight="1">
       <c r="A147" s="8" t="inlineStr">
         <is>
-          <t>Addison Fairfax (DBZ)</t>
+          <t>Avery Radcliffe (DBZ)</t>
         </is>
       </c>
       <c r="B147" s="8" t="inlineStr">
@@ -12407,9 +12485,9 @@
           <t>Rory Sanderson</t>
         </is>
       </c>
-      <c r="D147" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="D147" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="E147" s="9" t="inlineStr">
@@ -12427,24 +12505,24 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="H147" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="I147" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="J147" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="K147" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="H147" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="I147" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="J147" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="K147" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="L147" s="9" t="inlineStr">
@@ -12462,26 +12540,26 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="O147" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="P147" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="Q147" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="O147" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="P147" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="Q147" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
     </row>
     <row r="148" ht="16" customHeight="1">
       <c r="A148" s="8" t="inlineStr">
         <is>
-          <t>Avery Radcliffe (DBZ)</t>
+          <t>Cameron Hollings (DBZ)</t>
         </is>
       </c>
       <c r="B148" s="8" t="inlineStr">
@@ -12514,9 +12592,9 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="H148" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="H148" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="I148" s="10" t="inlineStr">
@@ -12524,9 +12602,9 @@
           <t>WO</t>
         </is>
       </c>
-      <c r="J148" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="J148" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="K148" s="9" t="inlineStr">
@@ -12549,9 +12627,9 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="O148" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="O148" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="P148" s="10" t="inlineStr">
@@ -12559,16 +12637,16 @@
           <t>WO</t>
         </is>
       </c>
-      <c r="Q148" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="Q148" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
     </row>
     <row r="149" ht="16" customHeight="1">
       <c r="A149" s="8" t="inlineStr">
         <is>
-          <t>Cameron Hollings (DBZ)</t>
+          <t>Darcy Langley (DBZ)</t>
         </is>
       </c>
       <c r="B149" s="8" t="inlineStr">
@@ -12655,7 +12733,7 @@
     <row r="150" ht="16" customHeight="1">
       <c r="A150" s="8" t="inlineStr">
         <is>
-          <t>Darcy Langley (DBZ)</t>
+          <t>Eden Beaumont (DBZ)</t>
         </is>
       </c>
       <c r="B150" s="8" t="inlineStr">
@@ -12742,7 +12820,7 @@
     <row r="151" ht="16" customHeight="1">
       <c r="A151" s="8" t="inlineStr">
         <is>
-          <t>Eden Beaumont (DBZ)</t>
+          <t>Finley Radcliffe (DBZ)</t>
         </is>
       </c>
       <c r="B151" s="8" t="inlineStr">
@@ -12760,14 +12838,14 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="E151" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="F151" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="E151" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="F151" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="G151" s="9" t="inlineStr">
@@ -12780,14 +12858,14 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="I151" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="J151" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="I151" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="J151" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="K151" s="9" t="inlineStr">
@@ -12795,14 +12873,14 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="L151" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="M151" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="L151" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="M151" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="N151" s="9" t="inlineStr">
@@ -12815,21 +12893,21 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="P151" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="Q151" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="P151" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="Q151" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
     </row>
     <row r="152" ht="16" customHeight="1">
       <c r="A152" s="8" t="inlineStr">
         <is>
-          <t>Finley Radcliffe (DBZ)</t>
+          <t>Hollis Radcliffe (DBZ)</t>
         </is>
       </c>
       <c r="B152" s="8" t="inlineStr">
@@ -12916,7 +12994,7 @@
     <row r="153" ht="16" customHeight="1">
       <c r="A153" s="8" t="inlineStr">
         <is>
-          <t>Hollis Radcliffe (DBZ)</t>
+          <t>Indigo Clarke (DBZ)</t>
         </is>
       </c>
       <c r="B153" s="8" t="inlineStr">
@@ -12934,14 +13012,14 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="E153" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="F153" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="E153" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="F153" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="G153" s="9" t="inlineStr">
@@ -12954,14 +13032,14 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="I153" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="J153" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="I153" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="J153" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="K153" s="9" t="inlineStr">
@@ -12969,14 +13047,14 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="L153" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="M153" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="L153" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="M153" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="N153" s="9" t="inlineStr">
@@ -12989,21 +13067,21 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="P153" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="Q153" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="P153" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="Q153" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
     </row>
     <row r="154" ht="16" customHeight="1">
       <c r="A154" s="8" t="inlineStr">
         <is>
-          <t>Indigo Clarke (DBZ)</t>
+          <t>Jordan Walsh (DBZ)</t>
         </is>
       </c>
       <c r="B154" s="8" t="inlineStr">
@@ -13036,9 +13114,9 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="H154" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="H154" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="I154" s="10" t="inlineStr">
@@ -13046,9 +13124,9 @@
           <t>WO</t>
         </is>
       </c>
-      <c r="J154" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="J154" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="K154" s="9" t="inlineStr">
@@ -13071,9 +13149,9 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="O154" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="O154" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="P154" s="10" t="inlineStr">
@@ -13081,16 +13159,16 @@
           <t>WO</t>
         </is>
       </c>
-      <c r="Q154" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="Q154" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
     </row>
     <row r="155" ht="16" customHeight="1">
       <c r="A155" s="8" t="inlineStr">
         <is>
-          <t>Jordan Walsh (DBZ)</t>
+          <t>Jules Pembroke (DBZ)</t>
         </is>
       </c>
       <c r="B155" s="8" t="inlineStr">
@@ -13103,9 +13181,9 @@
           <t>Rory Sanderson</t>
         </is>
       </c>
-      <c r="D155" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="D155" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="E155" s="9" t="inlineStr">
@@ -13123,24 +13201,24 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="H155" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="I155" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="J155" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="K155" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="H155" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="I155" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="J155" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="K155" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="L155" s="9" t="inlineStr">
@@ -13158,26 +13236,26 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="O155" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="P155" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="Q155" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="O155" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="P155" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="Q155" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
     </row>
     <row r="156" ht="16" customHeight="1">
       <c r="A156" s="8" t="inlineStr">
         <is>
-          <t>Jules Pembroke (DBZ)</t>
+          <t>Winter Clarke (DBZ)</t>
         </is>
       </c>
       <c r="B156" s="8" t="inlineStr">
@@ -13190,9 +13268,9 @@
           <t>Rory Sanderson</t>
         </is>
       </c>
-      <c r="D156" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="D156" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="E156" s="9" t="inlineStr">
@@ -13200,14 +13278,14 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="F156" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="G156" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="F156" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="G156" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="H156" s="9" t="inlineStr">
@@ -13220,14 +13298,14 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="J156" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="K156" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="J156" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="K156" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="L156" s="9" t="inlineStr">
@@ -13235,14 +13313,14 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="M156" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="N156" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="M156" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="N156" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="O156" s="9" t="inlineStr">
@@ -13255,16 +13333,16 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="Q156" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="Q156" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
     </row>
     <row r="157" ht="16" customHeight="1">
       <c r="A157" s="8" t="inlineStr">
         <is>
-          <t>Winter Clarke (DBZ)</t>
+          <t>Winter Grant (DBZ)</t>
         </is>
       </c>
       <c r="B157" s="8" t="inlineStr">
@@ -13277,9 +13355,9 @@
           <t>Rory Sanderson</t>
         </is>
       </c>
-      <c r="D157" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="D157" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="E157" s="9" t="inlineStr">
@@ -13287,14 +13365,14 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="F157" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="G157" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="F157" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="G157" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="H157" s="9" t="inlineStr">
@@ -13307,14 +13385,14 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="J157" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="K157" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="J157" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="K157" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="L157" s="9" t="inlineStr">
@@ -13322,14 +13400,14 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="M157" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="N157" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="M157" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="N157" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="O157" s="9" t="inlineStr">
@@ -13342,122 +13420,122 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="Q157" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="Q157" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
     </row>
     <row r="158" ht="16" customHeight="1">
-      <c r="A158" s="8" t="inlineStr">
-        <is>
-          <t>Winter Grant (DBZ)</t>
-        </is>
-      </c>
-      <c r="B158" s="8" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="C158" s="8" t="inlineStr">
-        <is>
-          <t>Rory Sanderson</t>
-        </is>
-      </c>
-      <c r="D158" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="E158" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="F158" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="G158" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="H158" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="I158" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="J158" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="K158" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="L158" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="M158" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="N158" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="O158" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="P158" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="Q158" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
+      <c r="A158" s="11" t="n"/>
+      <c r="B158" s="11" t="n"/>
+      <c r="C158" s="11" t="n"/>
+      <c r="D158" s="11" t="n"/>
+      <c r="E158" s="11" t="n"/>
+      <c r="F158" s="11" t="n"/>
+      <c r="G158" s="11" t="n"/>
+      <c r="H158" s="11" t="n"/>
+      <c r="I158" s="11" t="n"/>
+      <c r="J158" s="11" t="n"/>
+      <c r="K158" s="11" t="n"/>
+      <c r="L158" s="11" t="n"/>
+      <c r="M158" s="11" t="n"/>
+      <c r="N158" s="11" t="n"/>
+      <c r="O158" s="11" t="n"/>
+      <c r="P158" s="11" t="n"/>
+      <c r="Q158" s="11" t="n"/>
     </row>
     <row r="159" ht="4" customHeight="1">
-      <c r="A159" s="11" t="n"/>
-      <c r="B159" s="11" t="n"/>
-      <c r="C159" s="11" t="n"/>
-      <c r="D159" s="11" t="n"/>
-      <c r="E159" s="11" t="n"/>
-      <c r="F159" s="11" t="n"/>
-      <c r="G159" s="11" t="n"/>
-      <c r="H159" s="11" t="n"/>
-      <c r="I159" s="11" t="n"/>
-      <c r="J159" s="11" t="n"/>
-      <c r="K159" s="11" t="n"/>
-      <c r="L159" s="11" t="n"/>
-      <c r="M159" s="11" t="n"/>
-      <c r="N159" s="11" t="n"/>
-      <c r="O159" s="11" t="n"/>
-      <c r="P159" s="11" t="n"/>
-      <c r="Q159" s="11" t="n"/>
+      <c r="A159" s="8" t="inlineStr">
+        <is>
+          <t>Ashton Rowley (DBZ)</t>
+        </is>
+      </c>
+      <c r="B159" s="8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C159" s="8" t="inlineStr">
+        <is>
+          <t>Rowan Carter</t>
+        </is>
+      </c>
+      <c r="D159" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="E159" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="F159" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="G159" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="H159" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="I159" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="J159" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="K159" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="L159" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="M159" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="N159" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="O159" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="P159" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="Q159" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="16" customHeight="1">
       <c r="A160" s="8" t="inlineStr">
         <is>
-          <t>Ashton Rowley (DBZ)</t>
+          <t>Bailey Barrow (DBZ)</t>
         </is>
       </c>
       <c r="B160" s="8" t="inlineStr">
@@ -13544,7 +13622,7 @@
     <row r="161" ht="16" customHeight="1">
       <c r="A161" s="8" t="inlineStr">
         <is>
-          <t>Bailey Barrow (DBZ)</t>
+          <t>Cameron Alden (DBZ)</t>
         </is>
       </c>
       <c r="B161" s="8" t="inlineStr">
@@ -13572,24 +13650,24 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="G161" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="H161" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="I161" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="J161" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="G161" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="H161" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="I161" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="J161" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="K161" s="9" t="inlineStr">
@@ -13607,31 +13685,31 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="N161" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="O161" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="P161" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="Q161" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="N161" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="O161" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="P161" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="Q161" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
     </row>
     <row r="162" ht="16" customHeight="1">
       <c r="A162" s="8" t="inlineStr">
         <is>
-          <t>Cameron Alden (DBZ)</t>
+          <t>Cameron Hayes (DBZ)</t>
         </is>
       </c>
       <c r="B162" s="8" t="inlineStr">
@@ -13664,9 +13742,9 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="H162" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="H162" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="I162" s="10" t="inlineStr">
@@ -13674,9 +13752,9 @@
           <t>WO</t>
         </is>
       </c>
-      <c r="J162" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="J162" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="K162" s="9" t="inlineStr">
@@ -13699,9 +13777,9 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="O162" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="O162" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="P162" s="10" t="inlineStr">
@@ -13709,16 +13787,16 @@
           <t>WO</t>
         </is>
       </c>
-      <c r="Q162" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="Q162" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
     </row>
     <row r="163" ht="16" customHeight="1">
       <c r="A163" s="8" t="inlineStr">
         <is>
-          <t>Cameron Hayes (DBZ)</t>
+          <t>Perry Walker (DBZ)</t>
         </is>
       </c>
       <c r="B163" s="8" t="inlineStr">
@@ -13736,14 +13814,14 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="E163" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="F163" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="E163" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="F163" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="G163" s="9" t="inlineStr">
@@ -13751,14 +13829,14 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="H163" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="I163" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="H163" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="I163" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="J163" s="9" t="inlineStr">
@@ -13771,14 +13849,14 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="L163" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="M163" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="L163" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="M163" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="N163" s="9" t="inlineStr">
@@ -13786,14 +13864,14 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="O163" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="P163" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="O163" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="P163" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="Q163" s="9" t="inlineStr">
@@ -13805,7 +13883,7 @@
     <row r="164" ht="16" customHeight="1">
       <c r="A164" s="8" t="inlineStr">
         <is>
-          <t>Perry Walker (DBZ)</t>
+          <t>Sage Edwards (DBZ)</t>
         </is>
       </c>
       <c r="B164" s="8" t="inlineStr">
@@ -13818,19 +13896,19 @@
           <t>Rowan Carter</t>
         </is>
       </c>
-      <c r="D164" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="E164" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="F164" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="D164" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="E164" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="F164" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="G164" s="9" t="inlineStr">
@@ -13848,24 +13926,24 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="J164" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="K164" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="L164" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="M164" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="J164" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="K164" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="L164" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="M164" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="N164" s="9" t="inlineStr">
@@ -13883,16 +13961,16 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="Q164" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="Q164" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
     </row>
     <row r="165" ht="16" customHeight="1">
       <c r="A165" s="8" t="inlineStr">
         <is>
-          <t>Sage Edwards (DBZ)</t>
+          <t>Sam Jacobs (DBZ)</t>
         </is>
       </c>
       <c r="B165" s="8" t="inlineStr">
@@ -13905,9 +13983,9 @@
           <t>Rowan Carter</t>
         </is>
       </c>
-      <c r="D165" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="D165" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="E165" s="9" t="inlineStr">
@@ -13930,9 +14008,9 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="I165" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="I165" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="J165" s="10" t="inlineStr">
@@ -13940,9 +14018,9 @@
           <t>WO</t>
         </is>
       </c>
-      <c r="K165" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="K165" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="L165" s="9" t="inlineStr">
@@ -13965,9 +14043,9 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="P165" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="P165" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="Q165" s="10" t="inlineStr">
@@ -13979,7 +14057,7 @@
     <row r="166" ht="16" customHeight="1">
       <c r="A166" s="8" t="inlineStr">
         <is>
-          <t>Sam Jacobs (DBZ)</t>
+          <t>Skip Jackson (DBZ)</t>
         </is>
       </c>
       <c r="B166" s="8" t="inlineStr">
@@ -14066,7 +14144,7 @@
     <row r="167" ht="16" customHeight="1">
       <c r="A167" s="8" t="inlineStr">
         <is>
-          <t>Skip Jackson (DBZ)</t>
+          <t>Sully Roberts (DBZ)</t>
         </is>
       </c>
       <c r="B167" s="8" t="inlineStr">
@@ -14089,14 +14167,14 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="F167" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="G167" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="F167" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="G167" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="H167" s="9" t="inlineStr">
@@ -14104,14 +14182,14 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="I167" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="J167" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="I167" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="J167" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="K167" s="9" t="inlineStr">
@@ -14124,14 +14202,14 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="M167" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="N167" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="M167" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="N167" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="O167" s="9" t="inlineStr">
@@ -14139,21 +14217,21 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="P167" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="Q167" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="P167" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="Q167" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
     </row>
     <row r="168" ht="16" customHeight="1">
       <c r="A168" s="8" t="inlineStr">
         <is>
-          <t>Sully Roberts (DBZ)</t>
+          <t>Taylor Birken (DBZ)</t>
         </is>
       </c>
       <c r="B168" s="8" t="inlineStr">
@@ -14166,9 +14244,9 @@
           <t>Rowan Carter</t>
         </is>
       </c>
-      <c r="D168" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="D168" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="E168" s="9" t="inlineStr">
@@ -14176,14 +14254,14 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="F168" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="G168" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="F168" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="G168" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="H168" s="9" t="inlineStr">
@@ -14196,14 +14274,14 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="J168" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="K168" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="J168" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="K168" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="L168" s="9" t="inlineStr">
@@ -14211,14 +14289,14 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="M168" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="N168" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="M168" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="N168" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="O168" s="9" t="inlineStr">
@@ -14231,16 +14309,16 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="Q168" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="Q168" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
     </row>
     <row r="169" ht="16" customHeight="1">
       <c r="A169" s="8" t="inlineStr">
         <is>
-          <t>Taylor Birken (DBZ)</t>
+          <t>Vivian Burford (DBZ)</t>
         </is>
       </c>
       <c r="B169" s="8" t="inlineStr">
@@ -14253,81 +14331,81 @@
           <t>Rowan Carter</t>
         </is>
       </c>
-      <c r="D169" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="D169" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="E169" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="F169" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="G169" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="H169" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="G169" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="H169" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="I169" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="J169" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="K169" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="J169" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="K169" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="L169" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="M169" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="N169" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="O169" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="N169" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="O169" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="P169" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="Q169" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="Q169" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
         </is>
       </c>
     </row>
     <row r="170" ht="16" customHeight="1">
       <c r="A170" s="8" t="inlineStr">
         <is>
-          <t>Vivian Burford (DBZ)</t>
+          <t>Zephyr Langstone (DBZ)</t>
         </is>
       </c>
       <c r="B170" s="8" t="inlineStr">
@@ -14340,187 +14418,187 @@
           <t>Rowan Carter</t>
         </is>
       </c>
-      <c r="D170" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
+      <c r="D170" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="E170" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="F170" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="G170" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="H170" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="G170" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="H170" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="I170" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="J170" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="K170" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="J170" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="K170" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="L170" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="M170" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="N170" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="O170" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="N170" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="O170" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="P170" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="Q170" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="Q170" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
     </row>
     <row r="171" ht="16" customHeight="1">
-      <c r="A171" s="8" t="inlineStr">
-        <is>
-          <t>Zephyr Langstone (DBZ)</t>
-        </is>
-      </c>
-      <c r="B171" s="8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C171" s="8" t="inlineStr">
-        <is>
-          <t>Rowan Carter</t>
-        </is>
-      </c>
-      <c r="D171" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="E171" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="F171" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="G171" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="H171" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="I171" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="J171" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="K171" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="L171" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="M171" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="N171" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="O171" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="P171" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="Q171" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
+      <c r="A171" s="11" t="n"/>
+      <c r="B171" s="11" t="n"/>
+      <c r="C171" s="11" t="n"/>
+      <c r="D171" s="11" t="n"/>
+      <c r="E171" s="11" t="n"/>
+      <c r="F171" s="11" t="n"/>
+      <c r="G171" s="11" t="n"/>
+      <c r="H171" s="11" t="n"/>
+      <c r="I171" s="11" t="n"/>
+      <c r="J171" s="11" t="n"/>
+      <c r="K171" s="11" t="n"/>
+      <c r="L171" s="11" t="n"/>
+      <c r="M171" s="11" t="n"/>
+      <c r="N171" s="11" t="n"/>
+      <c r="O171" s="11" t="n"/>
+      <c r="P171" s="11" t="n"/>
+      <c r="Q171" s="11" t="n"/>
     </row>
     <row r="172" ht="4" customHeight="1">
-      <c r="A172" s="11" t="n"/>
-      <c r="B172" s="11" t="n"/>
-      <c r="C172" s="11" t="n"/>
-      <c r="D172" s="11" t="n"/>
-      <c r="E172" s="11" t="n"/>
-      <c r="F172" s="11" t="n"/>
-      <c r="G172" s="11" t="n"/>
-      <c r="H172" s="11" t="n"/>
-      <c r="I172" s="11" t="n"/>
-      <c r="J172" s="11" t="n"/>
-      <c r="K172" s="11" t="n"/>
-      <c r="L172" s="11" t="n"/>
-      <c r="M172" s="11" t="n"/>
-      <c r="N172" s="11" t="n"/>
-      <c r="O172" s="11" t="n"/>
-      <c r="P172" s="11" t="n"/>
-      <c r="Q172" s="11" t="n"/>
+      <c r="A172" s="8" t="inlineStr">
+        <is>
+          <t>Callum Marlowe (DBZ)</t>
+        </is>
+      </c>
+      <c r="B172" s="8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C172" s="8" t="inlineStr">
+        <is>
+          <t>Sage Turner</t>
+        </is>
+      </c>
+      <c r="D172" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="E172" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="F172" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="G172" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="H172" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="I172" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="J172" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="K172" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="L172" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="M172" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="N172" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="O172" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="P172" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="Q172" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="16" customHeight="1">
       <c r="A173" s="8" t="inlineStr">
         <is>
-          <t>Callum Marlowe (DBZ)</t>
+          <t>Jude Hartley (DBZ)</t>
         </is>
       </c>
       <c r="B173" s="8" t="inlineStr">
@@ -14538,24 +14616,24 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="E173" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="F173" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="G173" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="H173" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="E173" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="F173" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="G173" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="H173" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="I173" s="9" t="inlineStr">
@@ -14573,24 +14651,24 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="L173" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="M173" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="N173" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="O173" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="L173" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="M173" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="N173" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="O173" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="P173" s="9" t="inlineStr">
@@ -14607,7 +14685,7 @@
     <row r="174" ht="16" customHeight="1">
       <c r="A174" s="8" t="inlineStr">
         <is>
-          <t>Jude Hartley (DBZ)</t>
+          <t>Kendall Ashcroft (DBZ)</t>
         </is>
       </c>
       <c r="B174" s="8" t="inlineStr">
@@ -14625,14 +14703,14 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="E174" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="F174" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="E174" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="F174" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="G174" s="9" t="inlineStr">
@@ -14640,14 +14718,14 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="H174" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="I174" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="H174" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="I174" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="J174" s="9" t="inlineStr">
@@ -14660,14 +14738,14 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="L174" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="M174" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="L174" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="M174" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="N174" s="9" t="inlineStr">
@@ -14675,14 +14753,14 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="O174" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="P174" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="O174" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="P174" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="Q174" s="9" t="inlineStr">
@@ -14694,7 +14772,7 @@
     <row r="175" ht="16" customHeight="1">
       <c r="A175" s="8" t="inlineStr">
         <is>
-          <t>Kendall Ashcroft (DBZ)</t>
+          <t>Kris Winstanley (DBZ)</t>
         </is>
       </c>
       <c r="B175" s="8" t="inlineStr">
@@ -14709,79 +14787,79 @@
       </c>
       <c r="D175" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="E175" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="F175" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="E175" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="F175" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="G175" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="H175" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="I175" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="H175" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="I175" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="J175" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="K175" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="L175" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="M175" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="L175" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="M175" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="N175" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="O175" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="P175" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="O175" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="P175" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="Q175" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="176" ht="16" customHeight="1">
       <c r="A176" s="8" t="inlineStr">
         <is>
-          <t>Kris Winstanley (DBZ)</t>
+          <t>Lennox Darrow (DBZ)</t>
         </is>
       </c>
       <c r="B176" s="8" t="inlineStr">
@@ -14796,79 +14874,79 @@
       </c>
       <c r="D176" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="E176" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="F176" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="E176" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="F176" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="G176" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="H176" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="I176" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="H176" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="I176" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="J176" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="K176" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="L176" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="M176" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="L176" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="M176" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="N176" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="O176" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="P176" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="O176" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="P176" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="Q176" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
     </row>
     <row r="177" ht="16" customHeight="1">
       <c r="A177" s="8" t="inlineStr">
         <is>
-          <t>Lennox Darrow (DBZ)</t>
+          <t>Leslie Walsingham (DBZ)</t>
         </is>
       </c>
       <c r="B177" s="8" t="inlineStr">
@@ -14896,9 +14974,9 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="G177" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="G177" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="H177" s="10" t="inlineStr">
@@ -14906,9 +14984,9 @@
           <t>WO</t>
         </is>
       </c>
-      <c r="I177" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="I177" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="J177" s="9" t="inlineStr">
@@ -14931,9 +15009,9 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="N177" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="N177" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="O177" s="10" t="inlineStr">
@@ -14941,9 +15019,9 @@
           <t>WO</t>
         </is>
       </c>
-      <c r="P177" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="P177" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="Q177" s="9" t="inlineStr">
@@ -14955,7 +15033,7 @@
     <row r="178" ht="16" customHeight="1">
       <c r="A178" s="8" t="inlineStr">
         <is>
-          <t>Leslie Walsingham (DBZ)</t>
+          <t>Lindsay Wentworth (DBZ)</t>
         </is>
       </c>
       <c r="B178" s="8" t="inlineStr">
@@ -14973,24 +15051,24 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="E178" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="F178" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="G178" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="H178" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="E178" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="F178" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="G178" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="H178" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="I178" s="9" t="inlineStr">
@@ -15008,24 +15086,24 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="L178" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="M178" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="N178" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="O178" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="L178" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="M178" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="N178" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="O178" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="P178" s="9" t="inlineStr">
@@ -15042,7 +15120,7 @@
     <row r="179" ht="16" customHeight="1">
       <c r="A179" s="8" t="inlineStr">
         <is>
-          <t>Lindsay Wentworth (DBZ)</t>
+          <t>Merle Canning (DBZ)</t>
         </is>
       </c>
       <c r="B179" s="8" t="inlineStr">
@@ -15057,79 +15135,79 @@
       </c>
       <c r="D179" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="E179" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="F179" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="E179" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="F179" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="G179" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="H179" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="I179" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="J179" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="I179" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="J179" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="K179" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="L179" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="M179" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="L179" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="M179" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="N179" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="O179" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="P179" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="Q179" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="P179" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="Q179" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
     </row>
     <row r="180" ht="16" customHeight="1">
       <c r="A180" s="8" t="inlineStr">
         <is>
-          <t>Merle Canning (DBZ)</t>
+          <t>Nico Ellington (DBZ)</t>
         </is>
       </c>
       <c r="B180" s="8" t="inlineStr">
@@ -15142,34 +15220,34 @@
           <t>Sage Turner</t>
         </is>
       </c>
-      <c r="D180" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
+      <c r="D180" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="E180" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="F180" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="G180" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="H180" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="I180" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="I180" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="J180" s="10" t="inlineStr">
@@ -15177,34 +15255,34 @@
           <t>WO</t>
         </is>
       </c>
-      <c r="K180" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
+      <c r="K180" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="L180" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="M180" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="N180" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="O180" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="P180" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="P180" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="Q180" s="10" t="inlineStr">
@@ -15216,7 +15294,7 @@
     <row r="181" ht="16" customHeight="1">
       <c r="A181" s="8" t="inlineStr">
         <is>
-          <t>Nico Ellington (DBZ)</t>
+          <t>Rowan Ainsworth (DBZ)</t>
         </is>
       </c>
       <c r="B181" s="8" t="inlineStr">
@@ -15229,9 +15307,9 @@
           <t>Sage Turner</t>
         </is>
       </c>
-      <c r="D181" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="D181" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="E181" s="9" t="inlineStr">
@@ -15244,14 +15322,14 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="G181" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="H181" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="G181" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="H181" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="I181" s="9" t="inlineStr">
@@ -15259,14 +15337,14 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="J181" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="K181" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="J181" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="K181" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="L181" s="9" t="inlineStr">
@@ -15279,14 +15357,14 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="N181" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="O181" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="N181" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="O181" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="P181" s="9" t="inlineStr">
@@ -15294,16 +15372,16 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="Q181" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="Q181" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
     </row>
     <row r="182" ht="16" customHeight="1">
       <c r="A182" s="8" t="inlineStr">
         <is>
-          <t>Rowan Ainsworth (DBZ)</t>
+          <t>Sandy Lanchester (DBZ)</t>
         </is>
       </c>
       <c r="B182" s="8" t="inlineStr">
@@ -15326,9 +15404,9 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="F182" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="F182" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="G182" s="10" t="inlineStr">
@@ -15336,9 +15414,9 @@
           <t>WO</t>
         </is>
       </c>
-      <c r="H182" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="H182" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="I182" s="9" t="inlineStr">
@@ -15361,9 +15439,9 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="M182" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="M182" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="N182" s="10" t="inlineStr">
@@ -15371,9 +15449,9 @@
           <t>WO</t>
         </is>
       </c>
-      <c r="O182" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="O182" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="P182" s="9" t="inlineStr">
@@ -15390,7 +15468,7 @@
     <row r="183" ht="16" customHeight="1">
       <c r="A183" s="8" t="inlineStr">
         <is>
-          <t>Sandy Lanchester (DBZ)</t>
+          <t>York Selwyn (DBZ)</t>
         </is>
       </c>
       <c r="B183" s="8" t="inlineStr">
@@ -15413,14 +15491,14 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="F183" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="G183" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="F183" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="G183" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="H183" s="9" t="inlineStr">
@@ -15428,14 +15506,14 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="I183" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="J183" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="I183" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="J183" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="K183" s="9" t="inlineStr">
@@ -15448,14 +15526,14 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="M183" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="N183" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="M183" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="N183" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="O183" s="9" t="inlineStr">
@@ -15463,127 +15541,127 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="P183" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="Q183" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="P183" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="Q183" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
     </row>
     <row r="184" ht="16" customHeight="1">
-      <c r="A184" s="8" t="inlineStr">
-        <is>
-          <t>York Selwyn (DBZ)</t>
-        </is>
-      </c>
-      <c r="B184" s="8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C184" s="8" t="inlineStr">
-        <is>
-          <t>Sage Turner</t>
-        </is>
-      </c>
-      <c r="D184" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="E184" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="F184" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="G184" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="H184" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="I184" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="J184" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="K184" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="L184" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="M184" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="N184" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="O184" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="P184" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="Q184" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
+      <c r="A184" s="11" t="n"/>
+      <c r="B184" s="11" t="n"/>
+      <c r="C184" s="11" t="n"/>
+      <c r="D184" s="11" t="n"/>
+      <c r="E184" s="11" t="n"/>
+      <c r="F184" s="11" t="n"/>
+      <c r="G184" s="11" t="n"/>
+      <c r="H184" s="11" t="n"/>
+      <c r="I184" s="11" t="n"/>
+      <c r="J184" s="11" t="n"/>
+      <c r="K184" s="11" t="n"/>
+      <c r="L184" s="11" t="n"/>
+      <c r="M184" s="11" t="n"/>
+      <c r="N184" s="11" t="n"/>
+      <c r="O184" s="11" t="n"/>
+      <c r="P184" s="11" t="n"/>
+      <c r="Q184" s="11" t="n"/>
     </row>
     <row r="185" ht="4" customHeight="1">
-      <c r="A185" s="11" t="n"/>
-      <c r="B185" s="11" t="n"/>
-      <c r="C185" s="11" t="n"/>
-      <c r="D185" s="11" t="n"/>
-      <c r="E185" s="11" t="n"/>
-      <c r="F185" s="11" t="n"/>
-      <c r="G185" s="11" t="n"/>
-      <c r="H185" s="11" t="n"/>
-      <c r="I185" s="11" t="n"/>
-      <c r="J185" s="11" t="n"/>
-      <c r="K185" s="11" t="n"/>
-      <c r="L185" s="11" t="n"/>
-      <c r="M185" s="11" t="n"/>
-      <c r="N185" s="11" t="n"/>
-      <c r="O185" s="11" t="n"/>
-      <c r="P185" s="11" t="n"/>
-      <c r="Q185" s="11" t="n"/>
+      <c r="A185" s="8" t="inlineStr">
+        <is>
+          <t>Aubin Harcourt (DBZ)</t>
+        </is>
+      </c>
+      <c r="B185" s="8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C185" s="8" t="inlineStr">
+        <is>
+          <t>Sam Avery</t>
+        </is>
+      </c>
+      <c r="D185" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="E185" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="F185" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="G185" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="H185" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="I185" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="J185" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="K185" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="L185" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="M185" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="N185" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="O185" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="P185" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="Q185" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="16" customHeight="1">
       <c r="A186" s="8" t="inlineStr">
         <is>
-          <t>Aubin Harcourt (DBZ)</t>
+          <t>Avery Harrington (DBZ)</t>
         </is>
       </c>
       <c r="B186" s="8" t="inlineStr">
@@ -15601,14 +15679,14 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="E186" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="F186" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="E186" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="F186" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="G186" s="9" t="inlineStr">
@@ -15621,14 +15699,14 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="I186" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="J186" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="I186" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="J186" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="K186" s="9" t="inlineStr">
@@ -15636,14 +15714,14 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="L186" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="M186" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="L186" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="M186" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="N186" s="9" t="inlineStr">
@@ -15656,21 +15734,21 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="P186" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="Q186" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="P186" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="Q186" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
     </row>
     <row r="187" ht="16" customHeight="1">
       <c r="A187" s="8" t="inlineStr">
         <is>
-          <t>Avery Harrington (DBZ)</t>
+          <t>Brook Taverner (DBZ)</t>
         </is>
       </c>
       <c r="B187" s="8" t="inlineStr">
@@ -15757,7 +15835,7 @@
     <row r="188" ht="16" customHeight="1">
       <c r="A188" s="8" t="inlineStr">
         <is>
-          <t>Brook Taverner (DBZ)</t>
+          <t>Cassidy Luffman (DBZ)</t>
         </is>
       </c>
       <c r="B188" s="8" t="inlineStr">
@@ -15844,7 +15922,7 @@
     <row r="189" ht="16" customHeight="1">
       <c r="A189" s="8" t="inlineStr">
         <is>
-          <t>Cassidy Luffman (DBZ)</t>
+          <t>Gray Cartwright (DBZ)</t>
         </is>
       </c>
       <c r="B189" s="8" t="inlineStr">
@@ -15859,79 +15937,79 @@
       </c>
       <c r="D189" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="E189" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="F189" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="G189" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="F189" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="G189" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="H189" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="I189" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="J189" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="I189" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="J189" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="K189" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="L189" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="M189" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="N189" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="M189" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="N189" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="O189" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="P189" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="Q189" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="P189" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="Q189" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
         </is>
       </c>
     </row>
     <row r="190" ht="16" customHeight="1">
       <c r="A190" s="8" t="inlineStr">
         <is>
-          <t>Gray Cartwright (DBZ)</t>
+          <t>Harper Blake (DBZ)</t>
         </is>
       </c>
       <c r="B190" s="8" t="inlineStr">
@@ -15946,79 +16024,79 @@
       </c>
       <c r="D190" s="9" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="E190" s="9" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="F190" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="G190" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="F190" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="G190" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="H190" s="9" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="I190" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="J190" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="I190" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="J190" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="K190" s="9" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="L190" s="9" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="M190" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="N190" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="M190" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="N190" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="O190" s="9" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="P190" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="Q190" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="P190" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="Q190" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
     </row>
     <row r="191" ht="16" customHeight="1">
       <c r="A191" s="8" t="inlineStr">
         <is>
-          <t>Harper Blake (DBZ)</t>
+          <t>Lennox Pembroke (DBZ)</t>
         </is>
       </c>
       <c r="B191" s="8" t="inlineStr">
@@ -16031,81 +16109,81 @@
           <t>Sam Avery</t>
         </is>
       </c>
-      <c r="D191" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="E191" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
+      <c r="D191" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="E191" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="F191" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="G191" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="H191" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="I191" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="J191" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="K191" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="L191" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="I191" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="J191" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="K191" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="L191" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="M191" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="N191" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="O191" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="P191" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="Q191" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="P191" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="Q191" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="192" ht="16" customHeight="1">
       <c r="A192" s="8" t="inlineStr">
         <is>
-          <t>Lennox Pembroke (DBZ)</t>
+          <t>Monroe Lancaster (DBZ)</t>
         </is>
       </c>
       <c r="B192" s="8" t="inlineStr">
@@ -16118,81 +16196,81 @@
           <t>Sam Avery</t>
         </is>
       </c>
-      <c r="D192" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="E192" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="D192" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="E192" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="F192" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="G192" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="H192" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="I192" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="H192" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="I192" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="J192" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="K192" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="L192" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="K192" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="L192" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="M192" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="N192" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="O192" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="P192" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="O192" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="P192" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="Q192" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
     </row>
     <row r="193" ht="16" customHeight="1">
       <c r="A193" s="8" t="inlineStr">
         <is>
-          <t>Monroe Lancaster (DBZ)</t>
+          <t>Oakley Jackson (DBZ)</t>
         </is>
       </c>
       <c r="B193" s="8" t="inlineStr">
@@ -16205,9 +16283,9 @@
           <t>Sam Avery</t>
         </is>
       </c>
-      <c r="D193" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="D193" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="E193" s="9" t="inlineStr">
@@ -16225,24 +16303,24 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="H193" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="I193" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="J193" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="K193" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="H193" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="I193" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="J193" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="K193" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="L193" s="9" t="inlineStr">
@@ -16260,26 +16338,26 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="O193" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="P193" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="Q193" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="O193" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="P193" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="Q193" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
     </row>
     <row r="194" ht="16" customHeight="1">
       <c r="A194" s="8" t="inlineStr">
         <is>
-          <t>Oakley Jackson (DBZ)</t>
+          <t>Oliver Ashcombe (DBZ)</t>
         </is>
       </c>
       <c r="B194" s="8" t="inlineStr">
@@ -16366,7 +16444,7 @@
     <row r="195" ht="16" customHeight="1">
       <c r="A195" s="8" t="inlineStr">
         <is>
-          <t>Oliver Ashcombe (DBZ)</t>
+          <t>Robin Middleton (DBZ)</t>
         </is>
       </c>
       <c r="B195" s="8" t="inlineStr">
@@ -16379,34 +16457,34 @@
           <t>Sam Avery</t>
         </is>
       </c>
-      <c r="D195" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="D195" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="E195" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="F195" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="G195" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="H195" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="I195" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="I195" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="J195" s="10" t="inlineStr">
@@ -16414,34 +16492,34 @@
           <t>WO</t>
         </is>
       </c>
-      <c r="K195" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="K195" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="L195" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="M195" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="N195" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="O195" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="P195" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="P195" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="Q195" s="10" t="inlineStr">
@@ -16453,7 +16531,7 @@
     <row r="196" ht="16" customHeight="1">
       <c r="A196" s="8" t="inlineStr">
         <is>
-          <t>Robin Middleton (DBZ)</t>
+          <t>Wren Grant (DBZ)</t>
         </is>
       </c>
       <c r="B196" s="8" t="inlineStr">
@@ -16538,115 +16616,115 @@
       </c>
     </row>
     <row r="197" ht="16" customHeight="1">
-      <c r="A197" s="8" t="inlineStr">
-        <is>
-          <t>Wren Grant (DBZ)</t>
-        </is>
-      </c>
-      <c r="B197" s="8" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="C197" s="8" t="inlineStr">
-        <is>
-          <t>Sam Avery</t>
-        </is>
-      </c>
-      <c r="D197" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="E197" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="F197" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="G197" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="H197" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="I197" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="J197" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="K197" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="L197" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="M197" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="N197" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="O197" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="P197" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="Q197" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
+      <c r="A197" s="11" t="n"/>
+      <c r="B197" s="11" t="n"/>
+      <c r="C197" s="11" t="n"/>
+      <c r="D197" s="11" t="n"/>
+      <c r="E197" s="11" t="n"/>
+      <c r="F197" s="11" t="n"/>
+      <c r="G197" s="11" t="n"/>
+      <c r="H197" s="11" t="n"/>
+      <c r="I197" s="11" t="n"/>
+      <c r="J197" s="11" t="n"/>
+      <c r="K197" s="11" t="n"/>
+      <c r="L197" s="11" t="n"/>
+      <c r="M197" s="11" t="n"/>
+      <c r="N197" s="11" t="n"/>
+      <c r="O197" s="11" t="n"/>
+      <c r="P197" s="11" t="n"/>
+      <c r="Q197" s="11" t="n"/>
     </row>
     <row r="198" ht="4" customHeight="1">
-      <c r="A198" s="11" t="n"/>
-      <c r="B198" s="11" t="n"/>
-      <c r="C198" s="11" t="n"/>
-      <c r="D198" s="11" t="n"/>
-      <c r="E198" s="11" t="n"/>
-      <c r="F198" s="11" t="n"/>
-      <c r="G198" s="11" t="n"/>
-      <c r="H198" s="11" t="n"/>
-      <c r="I198" s="11" t="n"/>
-      <c r="J198" s="11" t="n"/>
-      <c r="K198" s="11" t="n"/>
-      <c r="L198" s="11" t="n"/>
-      <c r="M198" s="11" t="n"/>
-      <c r="N198" s="11" t="n"/>
-      <c r="O198" s="11" t="n"/>
-      <c r="P198" s="11" t="n"/>
-      <c r="Q198" s="11" t="n"/>
+      <c r="A198" s="8" t="inlineStr">
+        <is>
+          <t>Addison Treadwell (DBZ)</t>
+        </is>
+      </c>
+      <c r="B198" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C198" s="8" t="inlineStr">
+        <is>
+          <t>Sam Wetherall</t>
+        </is>
+      </c>
+      <c r="D198" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="E198" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="F198" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="G198" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="H198" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="I198" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="J198" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="K198" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="L198" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="M198" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="N198" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="O198" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="P198" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="Q198" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
     </row>
     <row r="199" ht="16" customHeight="1">
       <c r="A199" s="8" t="inlineStr">
         <is>
-          <t>Addison Treadwell (DBZ)</t>
+          <t>Alex Bramley (DBZ)</t>
         </is>
       </c>
       <c r="B199" s="8" t="inlineStr">
@@ -16679,9 +16757,9 @@
           <t>13:30-22:00</t>
         </is>
       </c>
-      <c r="H199" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="H199" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="I199" s="10" t="inlineStr">
@@ -16689,9 +16767,9 @@
           <t>WO</t>
         </is>
       </c>
-      <c r="J199" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
+      <c r="J199" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="K199" s="9" t="inlineStr">
@@ -16714,9 +16792,9 @@
           <t>13:30-22:00</t>
         </is>
       </c>
-      <c r="O199" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="O199" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="P199" s="10" t="inlineStr">
@@ -16724,16 +16802,16 @@
           <t>WO</t>
         </is>
       </c>
-      <c r="Q199" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
+      <c r="Q199" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
     </row>
     <row r="200" ht="16" customHeight="1">
       <c r="A200" s="8" t="inlineStr">
         <is>
-          <t>Alex Bramley (DBZ)</t>
+          <t>Andie Snowden (DBZ)</t>
         </is>
       </c>
       <c r="B200" s="8" t="inlineStr">
@@ -16756,14 +16834,14 @@
           <t>13:30-22:00</t>
         </is>
       </c>
-      <c r="F200" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="G200" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
+      <c r="F200" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="G200" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="H200" s="9" t="inlineStr">
@@ -16771,14 +16849,14 @@
           <t>13:30-22:00</t>
         </is>
       </c>
-      <c r="I200" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="J200" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="I200" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="J200" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="K200" s="9" t="inlineStr">
@@ -16791,14 +16869,14 @@
           <t>13:30-22:00</t>
         </is>
       </c>
-      <c r="M200" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="N200" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
+      <c r="M200" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="N200" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="O200" s="9" t="inlineStr">
@@ -16806,21 +16884,21 @@
           <t>13:30-22:00</t>
         </is>
       </c>
-      <c r="P200" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="Q200" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="P200" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="Q200" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="201" ht="16" customHeight="1">
       <c r="A201" s="8" t="inlineStr">
         <is>
-          <t>Andie Snowden (DBZ)</t>
+          <t>Blair Pembroke (DBZ)</t>
         </is>
       </c>
       <c r="B201" s="8" t="inlineStr">
@@ -16907,7 +16985,7 @@
     <row r="202" ht="16" customHeight="1">
       <c r="A202" s="8" t="inlineStr">
         <is>
-          <t>Blair Pembroke (DBZ)</t>
+          <t>Dale Norbury (DBZ)</t>
         </is>
       </c>
       <c r="B202" s="8" t="inlineStr">
@@ -16930,9 +17008,9 @@
           <t>13:30-22:00</t>
         </is>
       </c>
-      <c r="F202" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="F202" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="G202" s="10" t="inlineStr">
@@ -16940,9 +17018,9 @@
           <t>WO</t>
         </is>
       </c>
-      <c r="H202" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
+      <c r="H202" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="I202" s="9" t="inlineStr">
@@ -16965,9 +17043,9 @@
           <t>13:30-22:00</t>
         </is>
       </c>
-      <c r="M202" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="M202" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="N202" s="10" t="inlineStr">
@@ -16975,9 +17053,9 @@
           <t>WO</t>
         </is>
       </c>
-      <c r="O202" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
+      <c r="O202" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="P202" s="9" t="inlineStr">
@@ -16994,7 +17072,7 @@
     <row r="203" ht="16" customHeight="1">
       <c r="A203" s="8" t="inlineStr">
         <is>
-          <t>Dale Norbury (DBZ)</t>
+          <t>Emery Darrington (DBZ)</t>
         </is>
       </c>
       <c r="B203" s="8" t="inlineStr">
@@ -17007,9 +17085,9 @@
           <t>Sam Wetherall</t>
         </is>
       </c>
-      <c r="D203" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
+      <c r="D203" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="E203" s="9" t="inlineStr">
@@ -17017,19 +17095,19 @@
           <t>13:30-22:00</t>
         </is>
       </c>
-      <c r="F203" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="G203" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="H203" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="F203" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="G203" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="H203" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="I203" s="9" t="inlineStr">
@@ -17042,9 +17120,9 @@
           <t>13:30-22:00</t>
         </is>
       </c>
-      <c r="K203" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
+      <c r="K203" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="L203" s="9" t="inlineStr">
@@ -17052,19 +17130,19 @@
           <t>13:30-22:00</t>
         </is>
       </c>
-      <c r="M203" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="N203" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="O203" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="M203" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="N203" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="O203" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="P203" s="9" t="inlineStr">
@@ -17081,7 +17159,7 @@
     <row r="204" ht="16" customHeight="1">
       <c r="A204" s="8" t="inlineStr">
         <is>
-          <t>Emery Darrington (DBZ)</t>
+          <t>Erin Wycliffe (DBZ)</t>
         </is>
       </c>
       <c r="B204" s="8" t="inlineStr">
@@ -17094,9 +17172,9 @@
           <t>Sam Wetherall</t>
         </is>
       </c>
-      <c r="D204" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="D204" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="E204" s="9" t="inlineStr">
@@ -17104,19 +17182,19 @@
           <t>13:30-22:00</t>
         </is>
       </c>
-      <c r="F204" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="G204" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="H204" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
+      <c r="F204" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="G204" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="H204" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="I204" s="9" t="inlineStr">
@@ -17129,9 +17207,9 @@
           <t>13:30-22:00</t>
         </is>
       </c>
-      <c r="K204" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="K204" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="L204" s="9" t="inlineStr">
@@ -17139,19 +17217,19 @@
           <t>13:30-22:00</t>
         </is>
       </c>
-      <c r="M204" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="N204" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="O204" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
+      <c r="M204" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="N204" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="O204" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="P204" s="9" t="inlineStr">
@@ -17168,7 +17246,7 @@
     <row r="205" ht="16" customHeight="1">
       <c r="A205" s="8" t="inlineStr">
         <is>
-          <t>Erin Wycliffe (DBZ)</t>
+          <t>Gale Westbrook (DBZ)</t>
         </is>
       </c>
       <c r="B205" s="8" t="inlineStr">
@@ -17196,24 +17274,24 @@
           <t>13:30-22:00</t>
         </is>
       </c>
-      <c r="G205" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="H205" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="I205" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="J205" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
+      <c r="G205" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="H205" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="I205" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="J205" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="K205" s="9" t="inlineStr">
@@ -17231,31 +17309,31 @@
           <t>13:30-22:00</t>
         </is>
       </c>
-      <c r="N205" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="O205" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="P205" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="Q205" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
+      <c r="N205" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="O205" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="P205" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="Q205" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
     </row>
     <row r="206" ht="16" customHeight="1">
       <c r="A206" s="8" t="inlineStr">
         <is>
-          <t>Gale Westbrook (DBZ)</t>
+          <t>Laurie Blackwell (DBZ)</t>
         </is>
       </c>
       <c r="B206" s="8" t="inlineStr">
@@ -17342,7 +17420,7 @@
     <row r="207" ht="16" customHeight="1">
       <c r="A207" s="8" t="inlineStr">
         <is>
-          <t>Laurie Blackwell (DBZ)</t>
+          <t>Morgan Fairfax (DBZ)</t>
         </is>
       </c>
       <c r="B207" s="8" t="inlineStr">
@@ -17429,7 +17507,7 @@
     <row r="208" ht="16" customHeight="1">
       <c r="A208" s="8" t="inlineStr">
         <is>
-          <t>Morgan Fairfax (DBZ)</t>
+          <t>Riley Bennett (DBZ)</t>
         </is>
       </c>
       <c r="B208" s="8" t="inlineStr">
@@ -17516,7 +17594,7 @@
     <row r="209" ht="16" customHeight="1">
       <c r="A209" s="8" t="inlineStr">
         <is>
-          <t>Riley Bennett (DBZ)</t>
+          <t>Sidney Spencer (DBZ)</t>
         </is>
       </c>
       <c r="B209" s="8" t="inlineStr">
@@ -17544,24 +17622,24 @@
           <t>13:30-22:00</t>
         </is>
       </c>
-      <c r="G209" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="H209" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="I209" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="J209" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="G209" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="H209" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="I209" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="J209" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="K209" s="9" t="inlineStr">
@@ -17579,137 +17657,137 @@
           <t>13:30-22:00</t>
         </is>
       </c>
-      <c r="N209" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="O209" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="P209" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="Q209" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="N209" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="O209" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="P209" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="Q209" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="210" ht="16" customHeight="1">
-      <c r="A210" s="8" t="inlineStr">
-        <is>
-          <t>Sidney Spencer (DBZ)</t>
-        </is>
-      </c>
-      <c r="B210" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C210" s="8" t="inlineStr">
-        <is>
-          <t>Sam Wetherall</t>
-        </is>
-      </c>
-      <c r="D210" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="E210" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="F210" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="G210" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="H210" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="I210" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="J210" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="K210" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="L210" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="M210" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="N210" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="O210" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="P210" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="Q210" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
+      <c r="A210" s="11" t="n"/>
+      <c r="B210" s="11" t="n"/>
+      <c r="C210" s="11" t="n"/>
+      <c r="D210" s="11" t="n"/>
+      <c r="E210" s="11" t="n"/>
+      <c r="F210" s="11" t="n"/>
+      <c r="G210" s="11" t="n"/>
+      <c r="H210" s="11" t="n"/>
+      <c r="I210" s="11" t="n"/>
+      <c r="J210" s="11" t="n"/>
+      <c r="K210" s="11" t="n"/>
+      <c r="L210" s="11" t="n"/>
+      <c r="M210" s="11" t="n"/>
+      <c r="N210" s="11" t="n"/>
+      <c r="O210" s="11" t="n"/>
+      <c r="P210" s="11" t="n"/>
+      <c r="Q210" s="11" t="n"/>
     </row>
     <row r="211" ht="4" customHeight="1">
-      <c r="A211" s="11" t="n"/>
-      <c r="B211" s="11" t="n"/>
-      <c r="C211" s="11" t="n"/>
-      <c r="D211" s="11" t="n"/>
-      <c r="E211" s="11" t="n"/>
-      <c r="F211" s="11" t="n"/>
-      <c r="G211" s="11" t="n"/>
-      <c r="H211" s="11" t="n"/>
-      <c r="I211" s="11" t="n"/>
-      <c r="J211" s="11" t="n"/>
-      <c r="K211" s="11" t="n"/>
-      <c r="L211" s="11" t="n"/>
-      <c r="M211" s="11" t="n"/>
-      <c r="N211" s="11" t="n"/>
-      <c r="O211" s="11" t="n"/>
-      <c r="P211" s="11" t="n"/>
-      <c r="Q211" s="11" t="n"/>
+      <c r="A211" s="8" t="inlineStr">
+        <is>
+          <t>Eleri Bowden (DBZ)</t>
+        </is>
+      </c>
+      <c r="B211" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C211" s="8" t="inlineStr">
+        <is>
+          <t>Taylor Reed</t>
+        </is>
+      </c>
+      <c r="D211" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="E211" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="F211" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="G211" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="H211" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="I211" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="J211" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="K211" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="L211" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="M211" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="N211" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="O211" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="P211" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="Q211" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="16" customHeight="1">
       <c r="A212" s="8" t="inlineStr">
         <is>
-          <t>Eleri Bowden (DBZ)</t>
+          <t>Finley Marsh (DBZ)</t>
         </is>
       </c>
       <c r="B212" s="8" t="inlineStr">
@@ -17727,14 +17805,14 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="E212" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="F212" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
+      <c r="E212" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="F212" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="G212" s="9" t="inlineStr">
@@ -17742,14 +17820,14 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="H212" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="I212" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="H212" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="I212" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="J212" s="9" t="inlineStr">
@@ -17762,14 +17840,14 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="L212" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="M212" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
+      <c r="L212" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="M212" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="N212" s="9" t="inlineStr">
@@ -17777,14 +17855,14 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="O212" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="P212" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="O212" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="P212" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="Q212" s="9" t="inlineStr">
@@ -17796,7 +17874,7 @@
     <row r="213" ht="16" customHeight="1">
       <c r="A213" s="8" t="inlineStr">
         <is>
-          <t>Finley Marsh (DBZ)</t>
+          <t>Kendall Ross (DBZ)</t>
         </is>
       </c>
       <c r="B213" s="8" t="inlineStr">
@@ -17814,14 +17892,14 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="E213" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="F213" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="E213" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="F213" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="G213" s="9" t="inlineStr">
@@ -17834,14 +17912,14 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="I213" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="J213" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
+      <c r="I213" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="J213" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="K213" s="9" t="inlineStr">
@@ -17849,14 +17927,14 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="L213" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="M213" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="L213" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="M213" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="N213" s="9" t="inlineStr">
@@ -17869,21 +17947,21 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="P213" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="Q213" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
+      <c r="P213" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="Q213" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
     </row>
     <row r="214" ht="16" customHeight="1">
       <c r="A214" s="8" t="inlineStr">
         <is>
-          <t>Kendall Ross (DBZ)</t>
+          <t>Linden Bexley (DBZ)</t>
         </is>
       </c>
       <c r="B214" s="8" t="inlineStr">
@@ -17970,7 +18048,7 @@
     <row r="215" ht="16" customHeight="1">
       <c r="A215" s="8" t="inlineStr">
         <is>
-          <t>Linden Bexley (DBZ)</t>
+          <t>Noah Peckham (DBZ)</t>
         </is>
       </c>
       <c r="B215" s="8" t="inlineStr">
@@ -18003,14 +18081,14 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="H215" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="I215" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="H215" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="I215" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="J215" s="10" t="inlineStr">
@@ -18038,14 +18116,14 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="O215" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="P215" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="O215" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="P215" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="Q215" s="10" t="inlineStr">
@@ -18057,7 +18135,7 @@
     <row r="216" ht="16" customHeight="1">
       <c r="A216" s="8" t="inlineStr">
         <is>
-          <t>Noah Peckham (DBZ)</t>
+          <t>Remy Ashworth (DBZ)</t>
         </is>
       </c>
       <c r="B216" s="8" t="inlineStr">
@@ -18075,14 +18153,14 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="E216" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="F216" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
+      <c r="E216" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="F216" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="G216" s="9" t="inlineStr">
@@ -18090,9 +18168,9 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="H216" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="H216" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="I216" s="9" t="inlineStr">
@@ -18100,9 +18178,9 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="J216" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="J216" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="K216" s="9" t="inlineStr">
@@ -18110,14 +18188,14 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="L216" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="M216" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
+      <c r="L216" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="M216" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="N216" s="9" t="inlineStr">
@@ -18125,9 +18203,9 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="O216" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="O216" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="P216" s="9" t="inlineStr">
@@ -18135,16 +18213,16 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="Q216" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="Q216" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
         </is>
       </c>
     </row>
     <row r="217" ht="16" customHeight="1">
       <c r="A217" s="8" t="inlineStr">
         <is>
-          <t>Remy Ashworth (DBZ)</t>
+          <t>Sage Ellison (DBZ)</t>
         </is>
       </c>
       <c r="B217" s="8" t="inlineStr">
@@ -18162,14 +18240,14 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="E217" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="F217" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="E217" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="F217" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="G217" s="9" t="inlineStr">
@@ -18177,14 +18255,14 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="H217" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="I217" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
+      <c r="H217" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="I217" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="J217" s="9" t="inlineStr">
@@ -18197,14 +18275,14 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="L217" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="M217" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="L217" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="M217" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="N217" s="9" t="inlineStr">
@@ -18212,14 +18290,14 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="O217" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="P217" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
+      <c r="O217" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="P217" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="Q217" s="9" t="inlineStr">
@@ -18231,7 +18309,7 @@
     <row r="218" ht="16" customHeight="1">
       <c r="A218" s="8" t="inlineStr">
         <is>
-          <t>Sage Ellison (DBZ)</t>
+          <t>Shannon Elmsley (DBZ)</t>
         </is>
       </c>
       <c r="B218" s="8" t="inlineStr">
@@ -18318,7 +18396,7 @@
     <row r="219" ht="16" customHeight="1">
       <c r="A219" s="8" t="inlineStr">
         <is>
-          <t>Shannon Elmsley (DBZ)</t>
+          <t>Skyler Grant (DBZ)</t>
         </is>
       </c>
       <c r="B219" s="8" t="inlineStr">
@@ -18341,24 +18419,24 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="F219" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="G219" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="H219" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="I219" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="F219" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="G219" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="H219" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="I219" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="J219" s="9" t="inlineStr">
@@ -18376,24 +18454,24 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="M219" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="N219" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="O219" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="P219" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="M219" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="N219" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="O219" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="P219" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="Q219" s="9" t="inlineStr">
@@ -18405,7 +18483,7 @@
     <row r="220" ht="16" customHeight="1">
       <c r="A220" s="8" t="inlineStr">
         <is>
-          <t>Skyler Grant (DBZ)</t>
+          <t>Stevie Cresswell (DBZ)</t>
         </is>
       </c>
       <c r="B220" s="8" t="inlineStr">
@@ -18428,9 +18506,9 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="F220" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="F220" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="G220" s="10" t="inlineStr">
@@ -18438,9 +18516,9 @@
           <t>WO</t>
         </is>
       </c>
-      <c r="H220" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
+      <c r="H220" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="I220" s="9" t="inlineStr">
@@ -18463,9 +18541,9 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="M220" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="M220" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="N220" s="10" t="inlineStr">
@@ -18473,9 +18551,9 @@
           <t>WO</t>
         </is>
       </c>
-      <c r="O220" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
+      <c r="O220" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="P220" s="9" t="inlineStr">
@@ -18492,7 +18570,7 @@
     <row r="221" ht="16" customHeight="1">
       <c r="A221" s="8" t="inlineStr">
         <is>
-          <t>Stevie Cresswell (DBZ)</t>
+          <t>Taylor Hensley (DBZ)</t>
         </is>
       </c>
       <c r="B221" s="8" t="inlineStr">
@@ -18520,24 +18598,24 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="G221" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="H221" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="I221" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="J221" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
+      <c r="G221" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="H221" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="I221" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="J221" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="K221" s="9" t="inlineStr">
@@ -18555,31 +18633,31 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="N221" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="O221" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="P221" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="Q221" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
+      <c r="N221" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="O221" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="P221" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="Q221" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
     </row>
     <row r="222" ht="16" customHeight="1">
       <c r="A222" s="8" t="inlineStr">
         <is>
-          <t>Taylor Hensley (DBZ)</t>
+          <t>Tristan Whitfield (DBZ)</t>
         </is>
       </c>
       <c r="B222" s="8" t="inlineStr">
@@ -18612,9 +18690,9 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="H222" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
+      <c r="H222" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="I222" s="10" t="inlineStr">
@@ -18622,9 +18700,9 @@
           <t>WO</t>
         </is>
       </c>
-      <c r="J222" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="J222" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="K222" s="9" t="inlineStr">
@@ -18647,9 +18725,9 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="O222" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
+      <c r="O222" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="P222" s="10" t="inlineStr">
@@ -18657,99 +18735,13 @@
           <t>WO</t>
         </is>
       </c>
-      <c r="Q222" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-    </row>
-    <row r="223" ht="16" customHeight="1">
-      <c r="A223" s="8" t="inlineStr">
-        <is>
-          <t>Tristan Whitfield (DBZ)</t>
-        </is>
-      </c>
-      <c r="B223" s="8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C223" s="8" t="inlineStr">
-        <is>
-          <t>Taylor Reed</t>
-        </is>
-      </c>
-      <c r="D223" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="E223" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="F223" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="G223" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="H223" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="I223" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="J223" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="K223" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="L223" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="M223" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="N223" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="O223" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="P223" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="Q223" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-    </row>
+      <c r="Q222" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="16" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="K2:Q2"/>
@@ -18794,22 +18786,22 @@
           <t>KM — Roster 28 Sep – 11 Oct 2026 (30 agents)</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="2" t="n"/>
-      <c r="Q1" s="2" t="n"/>
+      <c r="B1" s="15" t="n"/>
+      <c r="C1" s="15" t="n"/>
+      <c r="D1" s="15" t="n"/>
+      <c r="E1" s="15" t="n"/>
+      <c r="F1" s="15" t="n"/>
+      <c r="G1" s="15" t="n"/>
+      <c r="H1" s="15" t="n"/>
+      <c r="I1" s="15" t="n"/>
+      <c r="J1" s="15" t="n"/>
+      <c r="K1" s="15" t="n"/>
+      <c r="L1" s="15" t="n"/>
+      <c r="M1" s="15" t="n"/>
+      <c r="N1" s="15" t="n"/>
+      <c r="O1" s="15" t="n"/>
+      <c r="P1" s="15" t="n"/>
+      <c r="Q1" s="16" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="n"/>
@@ -18820,23 +18812,23 @@
           <t>Week 1: 28 Sep – 4 Oct</t>
         </is>
       </c>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n"/>
-      <c r="I2" s="4" t="n"/>
-      <c r="J2" s="4" t="n"/>
+      <c r="E2" s="15" t="n"/>
+      <c r="F2" s="15" t="n"/>
+      <c r="G2" s="15" t="n"/>
+      <c r="H2" s="15" t="n"/>
+      <c r="I2" s="15" t="n"/>
+      <c r="J2" s="16" t="n"/>
       <c r="K2" s="5" t="inlineStr">
         <is>
           <t>Week 2: 5 Oct – 11 Oct</t>
         </is>
       </c>
-      <c r="L2" s="6" t="n"/>
-      <c r="M2" s="6" t="n"/>
-      <c r="N2" s="6" t="n"/>
-      <c r="O2" s="6" t="n"/>
-      <c r="P2" s="6" t="n"/>
-      <c r="Q2" s="6" t="n"/>
+      <c r="L2" s="15" t="n"/>
+      <c r="M2" s="15" t="n"/>
+      <c r="N2" s="15" t="n"/>
+      <c r="O2" s="15" t="n"/>
+      <c r="P2" s="15" t="n"/>
+      <c r="Q2" s="16" t="n"/>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
@@ -20470,12 +20462,12 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
@@ -20505,12 +20497,12 @@
       </c>
       <c r="N22" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="O22" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="P22" s="10" t="inlineStr">
@@ -21330,27 +21322,27 @@
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="J32" s="10" t="inlineStr">
@@ -21365,27 +21357,27 @@
       </c>
       <c r="L32" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="M32" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="N32" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="O32" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="P32" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="Q32" s="10" t="inlineStr">
@@ -21612,22 +21604,22 @@
           <t>Mirkl — Roster 28 Sep – 11 Oct 2026 (15 agents)</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="2" t="n"/>
-      <c r="Q1" s="2" t="n"/>
+      <c r="B1" s="15" t="n"/>
+      <c r="C1" s="15" t="n"/>
+      <c r="D1" s="15" t="n"/>
+      <c r="E1" s="15" t="n"/>
+      <c r="F1" s="15" t="n"/>
+      <c r="G1" s="15" t="n"/>
+      <c r="H1" s="15" t="n"/>
+      <c r="I1" s="15" t="n"/>
+      <c r="J1" s="15" t="n"/>
+      <c r="K1" s="15" t="n"/>
+      <c r="L1" s="15" t="n"/>
+      <c r="M1" s="15" t="n"/>
+      <c r="N1" s="15" t="n"/>
+      <c r="O1" s="15" t="n"/>
+      <c r="P1" s="15" t="n"/>
+      <c r="Q1" s="16" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="n"/>
@@ -21638,23 +21630,23 @@
           <t>Week 1: 28 Sep – 4 Oct</t>
         </is>
       </c>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n"/>
-      <c r="I2" s="4" t="n"/>
-      <c r="J2" s="4" t="n"/>
+      <c r="E2" s="15" t="n"/>
+      <c r="F2" s="15" t="n"/>
+      <c r="G2" s="15" t="n"/>
+      <c r="H2" s="15" t="n"/>
+      <c r="I2" s="15" t="n"/>
+      <c r="J2" s="16" t="n"/>
       <c r="K2" s="5" t="inlineStr">
         <is>
           <t>Week 2: 5 Oct – 11 Oct</t>
         </is>
       </c>
-      <c r="L2" s="6" t="n"/>
-      <c r="M2" s="6" t="n"/>
-      <c r="N2" s="6" t="n"/>
-      <c r="O2" s="6" t="n"/>
-      <c r="P2" s="6" t="n"/>
-      <c r="Q2" s="6" t="n"/>
+      <c r="L2" s="15" t="n"/>
+      <c r="M2" s="15" t="n"/>
+      <c r="N2" s="15" t="n"/>
+      <c r="O2" s="15" t="n"/>
+      <c r="P2" s="15" t="n"/>
+      <c r="Q2" s="16" t="n"/>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
@@ -21810,7 +21802,7 @@
       </c>
       <c r="K4" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="L4" s="10" t="inlineStr">
@@ -21820,7 +21812,7 @@
       </c>
       <c r="M4" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="N4" s="9" t="inlineStr">
@@ -21959,12 +21951,12 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
@@ -21974,12 +21966,12 @@
       </c>
       <c r="I6" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="J6" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -22210,12 +22202,12 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
@@ -22230,12 +22222,12 @@
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="J9" s="9" t="inlineStr">
@@ -23070,4 +23062,844 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>KM Rostered — Week 1 (28 Sep – 4 Oct) - 30 Agents</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>Shifts</t>
+        </is>
+      </c>
+      <c r="B2" s="18" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C2" s="18" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D2" s="18" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E2" s="18" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F2" s="18" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="G2" s="18" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="H2" s="18" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="F3" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G3" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" s="9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G4" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>23</v>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>27</v>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>KM Rostered — Week 2 (5 Oct – 11 Oct) - 30 Agents</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>Shifts</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="G10" s="18" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="H10" s="18" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="C15" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>21</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="H15" s="19" t="n">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>Mirkl Rostered — Week 1 (28 Sep – 4 Oct) - 15 Agents</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>Shifts</t>
+        </is>
+      </c>
+      <c r="B2" s="18" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C2" s="18" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D2" s="18" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E2" s="18" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F2" s="18" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="G2" s="18" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="H2" s="18" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" s="9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>Mirkl Rostered — Week 2 (5 Oct – 11 Oct) - 15 Agents</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>Shifts</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="G10" s="18" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="H10" s="18" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="C15" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="H15" s="19" t="n">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/2026-09-28/Roster_Sep28_Oct11_Full.xlsx
+++ b/2026-09-28/Roster_Sep28_Oct11_Full.xlsx
@@ -19143,7 +19143,7 @@
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>LEAVE</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
@@ -19153,7 +19153,7 @@
       </c>
       <c r="J6" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -19946,22 +19946,22 @@
       </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="M15" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="N15" s="9" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="O15" s="12" t="inlineStr">
         <is>
-          <t>LEAVE</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="P15" s="9" t="inlineStr">
@@ -20222,7 +20222,7 @@
       </c>
       <c r="O18" s="12" t="inlineStr">
         <is>
-          <t>LEAVE</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="P18" s="10" t="inlineStr">
@@ -20232,7 +20232,7 @@
       </c>
       <c r="Q18" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
     </row>
@@ -20410,22 +20410,22 @@
       </c>
       <c r="N21" s="12" t="inlineStr">
         <is>
-          <t>LEAVE</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="O21" s="12" t="inlineStr">
         <is>
-          <t>LEAVE</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="P21" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="Q21" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
     </row>
@@ -23164,7 +23164,7 @@
         <v>4</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -23276,7 +23276,7 @@
         <v>15</v>
       </c>
       <c r="H7" s="19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
@@ -23345,13 +23345,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" s="9" t="n">
         <v>8</v>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>9</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>6</v>
@@ -23360,7 +23360,7 @@
         <v>4</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -23413,10 +23413,10 @@
         <v>5</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -23457,22 +23457,22 @@
         <v>22</v>
       </c>
       <c r="C15" s="19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D15" s="19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E15" s="19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F15" s="19" t="n">
         <v>21</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H15" s="19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/2026-09-28/Roster_Sep28_Oct11_Full.xlsx
+++ b/2026-09-28/Roster_Sep28_Oct11_Full.xlsx
@@ -809,7 +809,7 @@
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="H4" s="10" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="I4" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="J4" s="9" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N4" s="9" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="O4" s="10" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="P4" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="Q4" s="9" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -1152,12 +1152,12 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="H8" s="9" t="inlineStr">
@@ -1172,12 +1172,12 @@
       </c>
       <c r="J8" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="K8" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="L8" s="9" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="M8" s="9" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="N8" s="9" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="O8" s="9" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="Q8" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="F19" s="10" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="L19" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="M19" s="10" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="N19" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="O19" s="9" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I21" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="N21" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="O21" s="10" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P21" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="Q21" s="9" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="H33" s="10" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="I33" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="J33" s="9" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="N33" s="9" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="O33" s="10" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="P33" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="Q33" s="9" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="H38" s="10" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="I38" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="J38" s="9" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="N38" s="9" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="O38" s="10" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="P38" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="Q38" s="9" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="H44" s="10" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="I44" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="J44" s="9" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="N44" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="O44" s="10" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="P44" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="Q44" s="9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="G46" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="H46" s="10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="J46" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="K46" s="9" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="N46" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="O46" s="10" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="Q46" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>08:00-16:30</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G47" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="H47" s="10" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="I47" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="J47" s="9" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="N47" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="O47" s="10" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="P47" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="Q47" s="9" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="E50" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="G50" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="H50" s="9" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="L50" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="M50" s="10" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="N50" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="O50" s="9" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="F56" s="9" t="inlineStr">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="G56" s="9" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="H56" s="9" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="L56" s="9" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="M56" s="9" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="N56" s="9" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="O56" s="9" t="inlineStr">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="G76" s="9" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="H76" s="10" t="inlineStr">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="I76" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="J76" s="9" t="inlineStr">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="N76" s="9" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="O76" s="10" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="P76" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="Q76" s="9" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="G93" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="H93" s="10" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="I93" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="J93" s="9" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="N93" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="O93" s="10" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="P93" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="Q93" s="9" t="inlineStr">
@@ -11613,7 +11613,7 @@
       </c>
       <c r="G136" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="H136" s="10" t="inlineStr">
@@ -11628,7 +11628,7 @@
       </c>
       <c r="J136" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="K136" s="9" t="inlineStr">
@@ -11648,7 +11648,7 @@
       </c>
       <c r="N136" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="O136" s="10" t="inlineStr">
@@ -11663,7 +11663,7 @@
       </c>
       <c r="Q136" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>08:00-16:30</t>
         </is>
       </c>
     </row>
@@ -18078,7 +18078,7 @@
       </c>
       <c r="G215" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="H215" s="10" t="inlineStr">
@@ -18093,7 +18093,7 @@
       </c>
       <c r="J215" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="K215" s="9" t="inlineStr">
@@ -18113,7 +18113,7 @@
       </c>
       <c r="N215" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="O215" s="10" t="inlineStr">
@@ -18128,7 +18128,7 @@
       </c>
       <c r="Q215" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>08:00-16:30</t>
         </is>
       </c>
     </row>

--- a/2026-09-28/Roster_Sep28_Oct11_Full.xlsx
+++ b/2026-09-28/Roster_Sep28_Oct11_Full.xlsx
@@ -9043,12 +9043,12 @@
       </c>
       <c r="I104" s="10" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="J104" s="10" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="K104" s="9" t="inlineStr">
@@ -20984,22 +20984,22 @@
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="I28" s="12" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="J28" s="12" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="K28" s="9" t="inlineStr">
@@ -21802,7 +21802,7 @@
       </c>
       <c r="K4" s="10" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="L4" s="10" t="inlineStr">
@@ -23089,13 +23089,13 @@
           <t>KM Rostered — Week 1 (28 Sep – 4 Oct) - 30 Agents</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
+      <c r="B1" s="15" t="n"/>
+      <c r="C1" s="15" t="n"/>
+      <c r="D1" s="15" t="n"/>
+      <c r="E1" s="15" t="n"/>
+      <c r="F1" s="15" t="n"/>
+      <c r="G1" s="15" t="n"/>
+      <c r="H1" s="16" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="18" t="inlineStr">
@@ -23285,13 +23285,13 @@
           <t>KM Rostered — Week 2 (5 Oct – 11 Oct) - 30 Agents</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="2" t="n"/>
-      <c r="H9" s="2" t="n"/>
+      <c r="B9" s="15" t="n"/>
+      <c r="C9" s="15" t="n"/>
+      <c r="D9" s="15" t="n"/>
+      <c r="E9" s="15" t="n"/>
+      <c r="F9" s="15" t="n"/>
+      <c r="G9" s="15" t="n"/>
+      <c r="H9" s="16" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="18" t="inlineStr">
@@ -23509,13 +23509,13 @@
           <t>Mirkl Rostered — Week 1 (28 Sep – 4 Oct) - 15 Agents</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
+      <c r="B1" s="15" t="n"/>
+      <c r="C1" s="15" t="n"/>
+      <c r="D1" s="15" t="n"/>
+      <c r="E1" s="15" t="n"/>
+      <c r="F1" s="15" t="n"/>
+      <c r="G1" s="15" t="n"/>
+      <c r="H1" s="16" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="18" t="inlineStr">
@@ -23705,13 +23705,13 @@
           <t>Mirkl Rostered — Week 2 (5 Oct – 11 Oct) - 15 Agents</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="2" t="n"/>
-      <c r="H9" s="2" t="n"/>
+      <c r="B9" s="15" t="n"/>
+      <c r="C9" s="15" t="n"/>
+      <c r="D9" s="15" t="n"/>
+      <c r="E9" s="15" t="n"/>
+      <c r="F9" s="15" t="n"/>
+      <c r="G9" s="15" t="n"/>
+      <c r="H9" s="16" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="18" t="inlineStr">

--- a/2026-09-28/Roster_Sep28_Oct11_Full.xlsx
+++ b/2026-09-28/Roster_Sep28_Oct11_Full.xlsx
@@ -23089,13 +23089,13 @@
           <t>KM Rostered — Week 1 (28 Sep – 4 Oct) - 30 Agents</t>
         </is>
       </c>
-      <c r="B1" s="15" t="n"/>
-      <c r="C1" s="15" t="n"/>
-      <c r="D1" s="15" t="n"/>
-      <c r="E1" s="15" t="n"/>
-      <c r="F1" s="15" t="n"/>
-      <c r="G1" s="15" t="n"/>
-      <c r="H1" s="16" t="n"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="18" t="inlineStr">
@@ -23155,16 +23155,16 @@
         <v>5</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -23267,16 +23267,16 @@
         <v>23</v>
       </c>
       <c r="E7" s="19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H7" s="19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
@@ -23285,13 +23285,13 @@
           <t>KM Rostered — Week 2 (5 Oct – 11 Oct) - 30 Agents</t>
         </is>
       </c>
-      <c r="B9" s="15" t="n"/>
-      <c r="C9" s="15" t="n"/>
-      <c r="D9" s="15" t="n"/>
-      <c r="E9" s="15" t="n"/>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
-      <c r="H9" s="16" t="n"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="18" t="inlineStr">
@@ -23509,13 +23509,13 @@
           <t>Mirkl Rostered — Week 1 (28 Sep – 4 Oct) - 15 Agents</t>
         </is>
       </c>
-      <c r="B1" s="15" t="n"/>
-      <c r="C1" s="15" t="n"/>
-      <c r="D1" s="15" t="n"/>
-      <c r="E1" s="15" t="n"/>
-      <c r="F1" s="15" t="n"/>
-      <c r="G1" s="15" t="n"/>
-      <c r="H1" s="16" t="n"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="18" t="inlineStr">
@@ -23705,13 +23705,13 @@
           <t>Mirkl Rostered — Week 2 (5 Oct – 11 Oct) - 15 Agents</t>
         </is>
       </c>
-      <c r="B9" s="15" t="n"/>
-      <c r="C9" s="15" t="n"/>
-      <c r="D9" s="15" t="n"/>
-      <c r="E9" s="15" t="n"/>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
-      <c r="H9" s="16" t="n"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="18" t="inlineStr">
@@ -23762,7 +23762,7 @@
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>0</v>
@@ -23874,7 +23874,7 @@
         </is>
       </c>
       <c r="B15" s="19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C15" s="19" t="n">
         <v>10</v>

--- a/2026-09-28/Roster_Sep28_Oct11_Full.xlsx
+++ b/2026-09-28/Roster_Sep28_Oct11_Full.xlsx
@@ -10,8 +10,6 @@
     <sheet name="DBZ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="KM" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Mirkl" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="KM Shift Snapshot" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Mirkl Shift Snapshot" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18758,6 +18756,3218 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:Q50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>KM — Roster 28 Sep – 11 Oct 2026 (30 agents)</t>
+        </is>
+      </c>
+      <c r="B1" s="15" t="n"/>
+      <c r="C1" s="15" t="n"/>
+      <c r="D1" s="15" t="n"/>
+      <c r="E1" s="15" t="n"/>
+      <c r="F1" s="15" t="n"/>
+      <c r="G1" s="15" t="n"/>
+      <c r="H1" s="15" t="n"/>
+      <c r="I1" s="15" t="n"/>
+      <c r="J1" s="15" t="n"/>
+      <c r="K1" s="15" t="n"/>
+      <c r="L1" s="15" t="n"/>
+      <c r="M1" s="15" t="n"/>
+      <c r="N1" s="15" t="n"/>
+      <c r="O1" s="15" t="n"/>
+      <c r="P1" s="15" t="n"/>
+      <c r="Q1" s="16" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Week 1: 28 Sep – 4 Oct</t>
+        </is>
+      </c>
+      <c r="E2" s="15" t="n"/>
+      <c r="F2" s="15" t="n"/>
+      <c r="G2" s="15" t="n"/>
+      <c r="H2" s="15" t="n"/>
+      <c r="I2" s="15" t="n"/>
+      <c r="J2" s="16" t="n"/>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Week 2: 5 Oct – 11 Oct</t>
+        </is>
+      </c>
+      <c r="L2" s="15" t="n"/>
+      <c r="M2" s="15" t="n"/>
+      <c r="N2" s="15" t="n"/>
+      <c r="O2" s="15" t="n"/>
+      <c r="P2" s="15" t="n"/>
+      <c r="Q2" s="16" t="n"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Agent Name</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Team No</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Team Lead</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Mon
+9/28</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Tue
+9/29</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>Wed
+9/30</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Thu
+10/1</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Fri
+10/2</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>Sat
+10/3</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>Sun
+10/4</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>Mon
+10/5</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>Tue
+10/6</t>
+        </is>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>Wed
+10/7</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="inlineStr">
+        <is>
+          <t>Thu
+10/8</t>
+        </is>
+      </c>
+      <c r="O3" s="7" t="inlineStr">
+        <is>
+          <t>Fri
+10/9</t>
+        </is>
+      </c>
+      <c r="P3" s="7" t="inlineStr">
+        <is>
+          <t>Sat
+10/10</t>
+        </is>
+      </c>
+      <c r="Q3" s="7" t="inlineStr">
+        <is>
+          <t>Sun
+10/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Arbor Webb (DBZ)</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Frankie Baxter</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="L4" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="M4" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="N4" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="O4" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="P4" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="Q4" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Bentley Fenton (DBZ)</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Frankie Baxter</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="M5" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="N5" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="O5" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="P5" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="Q5" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Charlie Penhaligon (DBZ)</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Frankie Baxter</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="M6" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="N6" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="O6" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="P6" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="Q6" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Cory Ashfield (DBZ)</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Frankie Baxter</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="M7" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="N7" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="O7" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="P7" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="Q7" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Ellis Harding (DBZ)</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Frankie Baxter</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="M8" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="O8" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="P8" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="Q8" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Emerys Talbot (DBZ)</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Frankie Baxter</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="M9" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="N9" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="O9" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="P9" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="Q9" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Finley Crossmoor (DBZ)</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Frankie Baxter</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="L10" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="N10" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="O10" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="P10" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="Q10" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Jordan Ashdown (DBZ)</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Frankie Baxter</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="M11" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="N11" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="O11" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="P11" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="Q11" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Joss Merriton (DBZ)</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Frankie Baxter</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="M12" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="N12" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="O12" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="P12" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="Q12" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Jules Beaumont (DBZ)</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Frankie Baxter</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="L13" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="N13" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="O13" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="P13" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="Q13" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Marley Whitcombe (DBZ)</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Frankie Baxter</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="K14" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="L14" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="M14" s="12" t="inlineStr">
+        <is>
+          <t>LEAVE</t>
+        </is>
+      </c>
+      <c r="N14" s="12" t="inlineStr">
+        <is>
+          <t>LEAVE</t>
+        </is>
+      </c>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t>LEAVE</t>
+        </is>
+      </c>
+      <c r="P14" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="Q14" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Riley Morton (DBZ)</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Frankie Baxter</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="L15" s="10" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="N15" s="9" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="O15" s="12" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="P15" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="Q15" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Robin Haversham (DBZ)</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Frankie Baxter</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="L16" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="M16" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="N16" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="O16" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="P16" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="Q16" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Sammy Pritchard (DBZ)</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Frankie Baxter</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="J17" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="K17" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="L17" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="M17" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="N17" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="O17" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="P17" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="Q17" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Vale Kingsnorth (DBZ)</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Frankie Baxter</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="J18" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="L18" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="M18" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="N18" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="O18" s="12" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="P18" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="Q18" s="10" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="4" customHeight="1">
+      <c r="A19" s="11" t="n"/>
+      <c r="B19" s="11" t="n"/>
+      <c r="C19" s="11" t="n"/>
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="11" t="n"/>
+      <c r="F19" s="11" t="n"/>
+      <c r="G19" s="11" t="n"/>
+      <c r="H19" s="11" t="n"/>
+      <c r="I19" s="11" t="n"/>
+      <c r="J19" s="11" t="n"/>
+      <c r="K19" s="11" t="n"/>
+      <c r="L19" s="11" t="n"/>
+      <c r="M19" s="11" t="n"/>
+      <c r="N19" s="11" t="n"/>
+      <c r="O19" s="11" t="n"/>
+      <c r="P19" s="11" t="n"/>
+      <c r="Q19" s="11" t="n"/>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Arden Scott (DBZ)</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Taylor Morgan</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="L20" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="M20" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="N20" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="O20" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="P20" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="Q20" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Blaine Whitmore (DBZ)</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Taylor Morgan</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="M21" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="N21" s="12" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="O21" s="12" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="P21" s="10" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="Q21" s="10" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Bryn Holmes (DBZ)</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Taylor Morgan</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="L22" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="M22" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="N22" s="10" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="O22" s="10" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="P22" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="Q22" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Cassidy Davies (DBZ)</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Taylor Morgan</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="J23" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="L23" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="M23" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="N23" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="O23" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="P23" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="Q23" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Clayton Jeffries (DBZ)</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Taylor Morgan</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="K24" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="L24" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="M24" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="N24" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="O24" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="P24" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="Q24" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Fletcher Loxley (DBZ)</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Taylor Morgan</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="L25" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="M25" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="N25" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="O25" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="P25" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="Q25" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>Hayden Cartwright (DBZ)</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Taylor Morgan</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="J26" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="K26" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="L26" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="M26" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="N26" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="O26" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="P26" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="Q26" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Marley Abbott (DBZ)</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Taylor Morgan</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="J27" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="K27" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="L27" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="M27" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="N27" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="O27" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="P27" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="Q27" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Marley Pritchard (DBZ)</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Taylor Morgan</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>LEAVE</t>
+        </is>
+      </c>
+      <c r="H28" s="12" t="inlineStr">
+        <is>
+          <t>LEAVE</t>
+        </is>
+      </c>
+      <c r="I28" s="12" t="inlineStr">
+        <is>
+          <t>LEAVE</t>
+        </is>
+      </c>
+      <c r="J28" s="12" t="inlineStr">
+        <is>
+          <t>LEAVE</t>
+        </is>
+      </c>
+      <c r="K28" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="L28" s="9" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="M28" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="N28" s="10" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="O28" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="P28" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="Q28" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Nico Ashford (DBZ)</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Taylor Morgan</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="K29" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="L29" s="9" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="M29" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="N29" s="10" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="O29" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="P29" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="Q29" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Reese Lambert (DBZ)</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Taylor Morgan</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="K30" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="L30" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="M30" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="N30" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="O30" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="P30" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="Q30" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Rory Fenton (DBZ)</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Taylor Morgan</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="K31" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="L31" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="M31" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="N31" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="O31" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="P31" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="Q31" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Rowan Fletcher (DBZ)</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Taylor Morgan</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="J32" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="K32" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="L32" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="M32" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="N32" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="O32" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="P32" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="Q32" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>Theo Ravenscroft (DBZ)</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Taylor Morgan</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="J33" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="L33" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="M33" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="N33" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="O33" s="12" t="inlineStr">
+        <is>
+          <t>LEAVE</t>
+        </is>
+      </c>
+      <c r="P33" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="Q33" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Walters (DBZ)</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Taylor Morgan</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="L34" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="M34" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="N34" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="O34" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="P34" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="Q34" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>KM Rostered — Week 1 (28 Sep – 4 Oct) - 30 Agents</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="n"/>
+      <c r="F36" s="2" t="n"/>
+      <c r="G36" s="2" t="n"/>
+      <c r="H36" s="2" t="n"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="18" t="inlineStr">
+        <is>
+          <t>Shifts</t>
+        </is>
+      </c>
+      <c r="B37" s="18" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D37" s="18" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E37" s="18" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F37" s="18" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="G37" s="18" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="H37" s="18" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C38" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F38" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G38" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H38" s="9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C39" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F39" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G39" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" s="9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C40" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F40" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G40" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H40" s="9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C41" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F41" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G41" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="H41" s="9" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B42" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="C42" s="19" t="n">
+        <v>23</v>
+      </c>
+      <c r="D42" s="19" t="n">
+        <v>23</v>
+      </c>
+      <c r="E42" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="F42" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="G42" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="H42" s="19" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="17" t="inlineStr">
+        <is>
+          <t>KM Rostered — Week 2 (5 Oct – 11 Oct) - 30 Agents</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n"/>
+      <c r="E44" s="2" t="n"/>
+      <c r="F44" s="2" t="n"/>
+      <c r="G44" s="2" t="n"/>
+      <c r="H44" s="2" t="n"/>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="18" t="inlineStr">
+        <is>
+          <t>Shifts</t>
+        </is>
+      </c>
+      <c r="B45" s="18" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D45" s="18" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E45" s="18" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F45" s="18" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="G45" s="18" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="H45" s="18" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C46" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E46" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F46" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G46" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H46" s="9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C47" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E47" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F47" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G47" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H47" s="9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C48" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D48" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E48" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F48" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G48" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H48" s="9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C49" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D49" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E49" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F49" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G49" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="H49" s="9" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B50" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="C50" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="D50" s="19" t="n">
+        <v>23</v>
+      </c>
+      <c r="E50" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="F50" s="19" t="n">
+        <v>21</v>
+      </c>
+      <c r="G50" s="19" t="n">
+        <v>17</v>
+      </c>
+      <c r="H50" s="19" t="n">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="D2:J2"/>
+    <mergeCell ref="K2:Q2"/>
+    <mergeCell ref="A1:Q1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -18781,9 +21991,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
-        <is>
-          <t>KM — Roster 28 Sep – 11 Oct 2026 (30 agents)</t>
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>Mirkl — Roster 28 Sep – 11 Oct 2026 (15 agents)</t>
         </is>
       </c>
       <c r="B1" s="15" t="n"/>
@@ -18934,27 +22144,27 @@
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>Arbor Webb (DBZ)</t>
+          <t>Bailey Whitmore (DBZ)</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Frankie Baxter</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
+          <t>Morgan Shaw</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
@@ -18967,14 +22177,14 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="I4" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="J4" s="9" t="inlineStr">
@@ -18982,19 +22192,19 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="L4" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>LEAVE</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="M4" s="9" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="N4" s="9" t="inlineStr">
@@ -19002,14 +22212,14 @@
           <t>07:00-15:30</t>
         </is>
       </c>
-      <c r="O4" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="P4" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="O4" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="P4" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="Q4" s="9" t="inlineStr">
@@ -19021,32 +22231,32 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Bentley Fenton (DBZ)</t>
+          <t>Carson Gardener (DBZ)</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Frankie Baxter</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
+          <t>Morgan Shaw</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
@@ -19064,24 +22274,24 @@
           <t>13:30-22:00</t>
         </is>
       </c>
-      <c r="J5" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="K5" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="L5" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="M5" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="L5" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="N5" s="9" t="inlineStr">
@@ -19099,86 +22309,86 @@
           <t>13:30-22:00</t>
         </is>
       </c>
-      <c r="Q5" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="Q5" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Charlie Penhaligon (DBZ)</t>
+          <t>Harlow Miller (DBZ)</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Frankie Baxter</t>
+          <t>Morgan Shaw</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="H6" s="12" t="inlineStr">
-        <is>
-          <t>WO</t>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="J6" s="10" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="M6" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="N6" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="O6" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="P6" s="10" t="inlineStr">
@@ -19195,104 +22405,104 @@
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Cory Ashfield (DBZ)</t>
+          <t>Hayden Burke (DBZ)</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Frankie Baxter</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+          <t>Morgan Shaw</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="J7" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="K7" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="L7" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="M7" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="N7" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="O7" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="O7" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="P7" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="Q7" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="Q7" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Ellis Harding (DBZ)</t>
+          <t>Lennox Clarke (DBZ)</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Frankie Baxter</t>
+          <t>Morgan Shaw</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
@@ -19302,27 +22512,27 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="J8" s="10" t="inlineStr">
@@ -19337,27 +22547,27 @@
       </c>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="M8" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="N8" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="O8" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="P8" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="Q8" s="10" t="inlineStr">
@@ -19369,27 +22579,27 @@
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Emerys Talbot (DBZ)</t>
+          <t>Leslie Jeffries (DBZ)</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Frankie Baxter</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
+          <t>Morgan Shaw</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>WO</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
@@ -19402,24 +22612,24 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="J9" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="K9" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="L9" s="9" t="inlineStr">
@@ -19437,41 +22647,41 @@
           <t>11:30-20:00</t>
         </is>
       </c>
-      <c r="O9" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="P9" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="Q9" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="O9" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="P9" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="Q9" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Finley Crossmoor (DBZ)</t>
+          <t>Nico Slater (DBZ)</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Frankie Baxter</t>
+          <t>Morgan Shaw</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
@@ -19486,27 +22696,27 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="J10" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="L10" s="10" t="inlineStr">
@@ -19521,64 +22731,64 @@
       </c>
       <c r="N10" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="O10" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="P10" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="Q10" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Jordan Ashdown (DBZ)</t>
+          <t>Oakley Montague (DBZ)</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Frankie Baxter</t>
+          <t>Morgan Shaw</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="H11" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
@@ -19586,34 +22796,34 @@
           <t>WO</t>
         </is>
       </c>
-      <c r="J11" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="L11" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="M11" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="N11" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="O11" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="O11" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="P11" s="10" t="inlineStr">
@@ -19621,56 +22831,56 @@
           <t>WO</t>
         </is>
       </c>
-      <c r="Q11" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+      <c r="Q11" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Joss Merriton (DBZ)</t>
+          <t>Palmer Clarke (DBZ)</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Frankie Baxter</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+          <t>Morgan Shaw</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="I12" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="J12" s="10" t="inlineStr">
@@ -19678,34 +22888,34 @@
           <t>WO</t>
         </is>
       </c>
-      <c r="K12" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+      <c r="K12" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="L12" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="M12" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="N12" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="O12" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="P12" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="P12" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="Q12" s="10" t="inlineStr">
@@ -19717,365 +22927,365 @@
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Jules Beaumont (DBZ)</t>
+          <t>Quinn Bellamy (DBZ)</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Frankie Baxter</t>
+          <t>Morgan Shaw</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="J13" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="K13" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="L13" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="M13" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="L13" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="M13" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="N13" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="O13" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="P13" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="O13" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="P13" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="Q13" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Marley Whitcombe (DBZ)</t>
+          <t>Reese Alderney (DBZ)</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Frankie Baxter</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+          <t>Morgan Shaw</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="J14" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="K14" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="L14" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="M14" s="12" t="inlineStr">
-        <is>
-          <t>LEAVE</t>
-        </is>
-      </c>
-      <c r="N14" s="12" t="inlineStr">
-        <is>
-          <t>LEAVE</t>
-        </is>
-      </c>
-      <c r="O14" s="12" t="inlineStr">
-        <is>
-          <t>LEAVE</t>
-        </is>
-      </c>
-      <c r="P14" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="Q14" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="M14" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="N14" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="O14" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="P14" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="Q14" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Riley Morton (DBZ)</t>
+          <t>Sage Redgrave (DBZ)</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Frankie Baxter</t>
+          <t>Morgan Shaw</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="J15" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="K15" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="L15" s="10" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="M15" s="10" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="M15" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="N15" s="9" t="inlineStr">
         <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="O15" s="12" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="P15" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="Q15" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="O15" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="P15" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="Q15" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Robin Haversham (DBZ)</t>
+          <t>Sasha Green (DBZ)</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Frankie Baxter</t>
+          <t>Morgan Shaw</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="I16" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="J16" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="K16" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="L16" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="M16" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="L16" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="M16" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="N16" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="O16" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="P16" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="Q16" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="P16" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="Q16" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Sammy Pritchard (DBZ)</t>
+          <t>Sloane Whittaker (DBZ)</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Frankie Baxter</t>
+          <t>Morgan Shaw</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
@@ -20152,3753 +23362,489 @@
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Vale Kingsnorth (DBZ)</t>
+          <t>Toby Worthington (DBZ)</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Frankie Baxter</t>
+          <t>Morgan Shaw</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="J18" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="K18" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="L18" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="M18" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="L18" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="M18" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
         </is>
       </c>
       <c r="N18" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="O18" s="12" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="P18" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="Q18" s="10" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="4" customHeight="1">
-      <c r="A19" s="11" t="n"/>
-      <c r="B19" s="11" t="n"/>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="11" t="n"/>
-      <c r="G19" s="11" t="n"/>
-      <c r="H19" s="11" t="n"/>
-      <c r="I19" s="11" t="n"/>
-      <c r="J19" s="11" t="n"/>
-      <c r="K19" s="11" t="n"/>
-      <c r="L19" s="11" t="n"/>
-      <c r="M19" s="11" t="n"/>
-      <c r="N19" s="11" t="n"/>
-      <c r="O19" s="11" t="n"/>
-      <c r="P19" s="11" t="n"/>
-      <c r="Q19" s="11" t="n"/>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>Arden Scott (DBZ)</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Taylor Morgan</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="E20" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="J20" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="K20" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="L20" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="M20" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="N20" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="O20" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="P20" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="Q20" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Blaine Whitmore (DBZ)</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>Taylor Morgan</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="F21" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="G21" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="H21" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="I21" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="J21" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="K21" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="L21" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="M21" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="N21" s="12" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="O21" s="12" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="P21" s="10" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="Q21" s="10" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>Bryn Holmes (DBZ)</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Taylor Morgan</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="I22" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="J22" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="K22" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="L22" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="M22" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="N22" s="10" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="O22" s="10" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="P22" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="Q22" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>Cassidy Davies (DBZ)</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>Taylor Morgan</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="H23" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="I23" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="J23" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="K23" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="L23" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="M23" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="N23" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="O23" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="P23" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="Q23" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>Clayton Jeffries (DBZ)</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>Taylor Morgan</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="H24" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="I24" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="J24" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="K24" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="L24" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="M24" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="N24" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="O24" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="P24" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="Q24" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>Fletcher Loxley (DBZ)</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Taylor Morgan</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="G25" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="H25" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="I25" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="J25" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="K25" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="L25" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="M25" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="N25" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="O25" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="P25" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="Q25" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>Hayden Cartwright (DBZ)</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>Taylor Morgan</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="G26" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="H26" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="I26" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="J26" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="K26" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="L26" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="M26" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="N26" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="O26" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="P26" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="Q26" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>Marley Abbott (DBZ)</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>Taylor Morgan</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="G27" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="H27" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="I27" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="J27" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="K27" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="L27" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="M27" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="N27" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="O27" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="P27" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="Q27" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>Marley Pritchard (DBZ)</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>Taylor Morgan</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="F28" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="G28" s="10" t="inlineStr">
-        <is>
-          <t>LEAVE</t>
-        </is>
-      </c>
-      <c r="H28" s="12" t="inlineStr">
-        <is>
-          <t>LEAVE</t>
-        </is>
-      </c>
-      <c r="I28" s="12" t="inlineStr">
-        <is>
-          <t>LEAVE</t>
-        </is>
-      </c>
-      <c r="J28" s="12" t="inlineStr">
-        <is>
-          <t>LEAVE</t>
-        </is>
-      </c>
-      <c r="K28" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="L28" s="9" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="M28" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="N28" s="10" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="O28" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="P28" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="Q28" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>Nico Ashford (DBZ)</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Taylor Morgan</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="F29" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="G29" s="10" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="H29" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="I29" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="J29" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="K29" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="L29" s="9" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="M29" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="N29" s="10" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="O29" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="P29" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="Q29" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>Reese Lambert (DBZ)</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>Taylor Morgan</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="G30" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="H30" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="I30" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="J30" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="K30" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="L30" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="M30" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="N30" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="O30" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="P30" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="Q30" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>Rory Fenton (DBZ)</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>Taylor Morgan</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="G31" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="H31" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="I31" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="J31" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="K31" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="L31" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="M31" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="N31" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="O31" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="P31" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="Q31" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>Rowan Fletcher (DBZ)</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>Taylor Morgan</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="G32" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="H32" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="J32" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="K32" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="L32" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="M32" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="N32" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="O32" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="P32" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="Q32" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>Theo Ravenscroft (DBZ)</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>Taylor Morgan</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="G33" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="H33" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="I33" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="J33" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="K33" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="L33" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="M33" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="N33" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="O33" s="12" t="inlineStr">
-        <is>
-          <t>LEAVE</t>
-        </is>
-      </c>
-      <c r="P33" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="Q33" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>Tyler Walters (DBZ)</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>Taylor Morgan</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="E34" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="F34" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="G34" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="H34" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="J34" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="K34" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="L34" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="M34" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="N34" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="O34" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="P34" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="Q34" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="O18" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="P18" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="Q18" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>Mirkl Rostered — Week 1 (28 Sep – 4 Oct) - 15 Agents</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>Shifts</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E21" s="18" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F21" s="18" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="G21" s="18" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="H21" s="18" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G23" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" s="9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H25" s="9" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="C26" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="D26" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="F26" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="G26" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="H26" s="19" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>Mirkl Rostered — Week 2 (5 Oct – 11 Oct) - 15 Agents</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+      <c r="E28" s="2" t="n"/>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="2" t="n"/>
+      <c r="H28" s="2" t="n"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>Shifts</t>
+        </is>
+      </c>
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D29" s="18" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E29" s="18" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F29" s="18" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="G29" s="18" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="H29" s="18" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" s="9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G31" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H31" s="9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F32" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G33" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H33" s="9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B34" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="C34" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="D34" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="F34" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="G34" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="H34" s="19" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="D2:J2"/>
     <mergeCell ref="K2:Q2"/>
     <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="D2:J2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
-        <is>
-          <t>Mirkl — Roster 28 Sep – 11 Oct 2026 (15 agents)</t>
-        </is>
-      </c>
-      <c r="B1" s="15" t="n"/>
-      <c r="C1" s="15" t="n"/>
-      <c r="D1" s="15" t="n"/>
-      <c r="E1" s="15" t="n"/>
-      <c r="F1" s="15" t="n"/>
-      <c r="G1" s="15" t="n"/>
-      <c r="H1" s="15" t="n"/>
-      <c r="I1" s="15" t="n"/>
-      <c r="J1" s="15" t="n"/>
-      <c r="K1" s="15" t="n"/>
-      <c r="L1" s="15" t="n"/>
-      <c r="M1" s="15" t="n"/>
-      <c r="N1" s="15" t="n"/>
-      <c r="O1" s="15" t="n"/>
-      <c r="P1" s="15" t="n"/>
-      <c r="Q1" s="16" t="n"/>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Week 1: 28 Sep – 4 Oct</t>
-        </is>
-      </c>
-      <c r="E2" s="15" t="n"/>
-      <c r="F2" s="15" t="n"/>
-      <c r="G2" s="15" t="n"/>
-      <c r="H2" s="15" t="n"/>
-      <c r="I2" s="15" t="n"/>
-      <c r="J2" s="16" t="n"/>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>Week 2: 5 Oct – 11 Oct</t>
-        </is>
-      </c>
-      <c r="L2" s="15" t="n"/>
-      <c r="M2" s="15" t="n"/>
-      <c r="N2" s="15" t="n"/>
-      <c r="O2" s="15" t="n"/>
-      <c r="P2" s="15" t="n"/>
-      <c r="Q2" s="16" t="n"/>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>Agent Name</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Team No</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>Team Lead</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>Mon
-9/28</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>Tue
-9/29</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>Wed
-9/30</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>Thu
-10/1</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>Fri
-10/2</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>Sat
-10/3</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="inlineStr">
-        <is>
-          <t>Sun
-10/4</t>
-        </is>
-      </c>
-      <c r="K3" s="7" t="inlineStr">
-        <is>
-          <t>Mon
-10/5</t>
-        </is>
-      </c>
-      <c r="L3" s="7" t="inlineStr">
-        <is>
-          <t>Tue
-10/6</t>
-        </is>
-      </c>
-      <c r="M3" s="7" t="inlineStr">
-        <is>
-          <t>Wed
-10/7</t>
-        </is>
-      </c>
-      <c r="N3" s="7" t="inlineStr">
-        <is>
-          <t>Thu
-10/8</t>
-        </is>
-      </c>
-      <c r="O3" s="7" t="inlineStr">
-        <is>
-          <t>Fri
-10/9</t>
-        </is>
-      </c>
-      <c r="P3" s="7" t="inlineStr">
-        <is>
-          <t>Sat
-10/10</t>
-        </is>
-      </c>
-      <c r="Q3" s="7" t="inlineStr">
-        <is>
-          <t>Sun
-10/11</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>Bailey Whitmore (DBZ)</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Morgan Shaw</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="H4" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="K4" s="10" t="inlineStr">
-        <is>
-          <t>LEAVE</t>
-        </is>
-      </c>
-      <c r="L4" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="M4" s="9" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="N4" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="O4" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="P4" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="Q4" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>Carson Gardener (DBZ)</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Morgan Shaw</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="H5" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="J5" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="K5" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="L5" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="M5" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="N5" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="O5" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="P5" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="Q5" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Harlow Miller (DBZ)</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Morgan Shaw</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="J6" s="10" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="K6" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="L6" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="M6" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="N6" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="O6" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="P6" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="Q6" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Hayden Burke (DBZ)</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Morgan Shaw</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="H7" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="J7" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="K7" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="L7" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="M7" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="N7" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="O7" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="P7" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="Q7" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Lennox Clarke (DBZ)</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Morgan Shaw</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="H8" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="J8" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="K8" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="L8" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="M8" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="N8" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="O8" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="P8" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="Q8" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Leslie Jeffries (DBZ)</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Morgan Shaw</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="H9" s="10" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="J9" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="K9" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="L9" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="M9" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="N9" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="O9" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="P9" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="Q9" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Nico Slater (DBZ)</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Morgan Shaw</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="H10" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="I10" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="J10" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="K10" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="L10" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="M10" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="N10" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="O10" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="P10" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="Q10" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Oakley Montague (DBZ)</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Morgan Shaw</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="I11" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="J11" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="K11" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="L11" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="M11" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="N11" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="O11" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="P11" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="Q11" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>Palmer Clarke (DBZ)</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Morgan Shaw</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="J12" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="K12" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="L12" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="M12" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="N12" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="O12" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="P12" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="Q12" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Quinn Bellamy (DBZ)</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Morgan Shaw</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="J13" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="K13" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="L13" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="M13" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="N13" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="O13" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="P13" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="Q13" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>Reese Alderney (DBZ)</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Morgan Shaw</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="J14" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="K14" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="L14" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="M14" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="N14" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="O14" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="P14" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="Q14" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>Sage Redgrave (DBZ)</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Morgan Shaw</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="I15" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="J15" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="K15" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="L15" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="M15" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="N15" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="O15" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="P15" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="Q15" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>Sasha Green (DBZ)</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Morgan Shaw</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="H16" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="J16" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="K16" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="L16" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="M16" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="N16" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="O16" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="P16" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="Q16" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>Sloane Whittaker (DBZ)</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Morgan Shaw</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="J17" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="K17" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="L17" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="M17" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="N17" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="O17" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="P17" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="Q17" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>Toby Worthington (DBZ)</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Morgan Shaw</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="J18" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="K18" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="L18" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="M18" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="N18" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="O18" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="P18" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="Q18" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="K2:Q2"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="D2:J2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="17" t="inlineStr">
-        <is>
-          <t>KM Rostered — Week 1 (28 Sep – 4 Oct) - 30 Agents</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="18" t="inlineStr">
-        <is>
-          <t>Shifts</t>
-        </is>
-      </c>
-      <c r="B2" s="18" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C2" s="18" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D2" s="18" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="E2" s="18" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="F2" s="18" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="G2" s="18" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="H2" s="18" t="inlineStr">
-        <is>
-          <t>Sun</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="C3" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="D3" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="E3" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="F3" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="G3" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H3" s="9" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="C4" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="D4" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F4" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="G4" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" s="9" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="C5" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G5" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" s="9" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G6" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H6" s="9" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="n">
-        <v>22</v>
-      </c>
-      <c r="C7" s="19" t="n">
-        <v>23</v>
-      </c>
-      <c r="D7" s="19" t="n">
-        <v>23</v>
-      </c>
-      <c r="E7" s="19" t="n">
-        <v>28</v>
-      </c>
-      <c r="F7" s="19" t="n">
-        <v>24</v>
-      </c>
-      <c r="G7" s="19" t="n">
-        <v>15</v>
-      </c>
-      <c r="H7" s="19" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>KM Rostered — Week 2 (5 Oct – 11 Oct) - 30 Agents</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="2" t="n"/>
-      <c r="H9" s="2" t="n"/>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
-        <is>
-          <t>Shifts</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="G10" s="18" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="H10" s="18" t="inlineStr">
-        <is>
-          <t>Sun</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="C11" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="G11" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="H11" s="9" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="G12" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H12" s="9" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="C13" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="G13" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H13" s="9" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="C14" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="F14" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="G14" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H14" s="9" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="n">
-        <v>22</v>
-      </c>
-      <c r="C15" s="19" t="n">
-        <v>24</v>
-      </c>
-      <c r="D15" s="19" t="n">
-        <v>23</v>
-      </c>
-      <c r="E15" s="19" t="n">
-        <v>26</v>
-      </c>
-      <c r="F15" s="19" t="n">
-        <v>21</v>
-      </c>
-      <c r="G15" s="19" t="n">
-        <v>17</v>
-      </c>
-      <c r="H15" s="19" t="n">
-        <v>13</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="17" t="inlineStr">
-        <is>
-          <t>Mirkl Rostered — Week 1 (28 Sep – 4 Oct) - 15 Agents</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="18" t="inlineStr">
-        <is>
-          <t>Shifts</t>
-        </is>
-      </c>
-      <c r="B2" s="18" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C2" s="18" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D2" s="18" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="E2" s="18" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="F2" s="18" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="G2" s="18" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="H2" s="18" t="inlineStr">
-        <is>
-          <t>Sun</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H3" s="9" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="F4" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="G4" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H4" s="9" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" s="9" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="C6" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H6" s="9" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="C7" s="19" t="n">
-        <v>9</v>
-      </c>
-      <c r="D7" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E7" s="19" t="n">
-        <v>13</v>
-      </c>
-      <c r="F7" s="19" t="n">
-        <v>11</v>
-      </c>
-      <c r="G7" s="19" t="n">
-        <v>11</v>
-      </c>
-      <c r="H7" s="19" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>Mirkl Rostered — Week 2 (5 Oct – 11 Oct) - 15 Agents</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="2" t="n"/>
-      <c r="H9" s="2" t="n"/>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
-        <is>
-          <t>Shifts</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="G10" s="18" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="H10" s="18" t="inlineStr">
-        <is>
-          <t>Sun</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G11" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H11" s="9" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="G12" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H12" s="9" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C13" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="9" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="C14" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="F14" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G14" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H14" s="9" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="n">
-        <v>11</v>
-      </c>
-      <c r="C15" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="D15" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="F15" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="G15" s="19" t="n">
-        <v>9</v>
-      </c>
-      <c r="H15" s="19" t="n">
-        <v>10</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/2026-09-28/Roster_Sep28_Oct11_Full.xlsx
+++ b/2026-09-28/Roster_Sep28_Oct11_Full.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +50,7 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font/>
   </fonts>
   <fills count="12">
     <fill>
@@ -119,7 +120,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -185,11 +186,12 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -234,6 +236,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7022,27 +7028,27 @@
       </c>
       <c r="M79" s="9" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="N79" s="9" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="O79" s="9" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="P79" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="Q79" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
     </row>
@@ -8760,12 +8766,12 @@
       </c>
       <c r="E101" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="G101" s="9" t="inlineStr">
@@ -8780,17 +8786,17 @@
       </c>
       <c r="I101" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="J101" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="K101" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="L101" s="10" t="inlineStr">
@@ -8805,12 +8811,12 @@
       </c>
       <c r="N101" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="O101" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="P101" s="9" t="inlineStr">
@@ -15322,22 +15328,22 @@
       </c>
       <c r="G181" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="H181" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="I181" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="J181" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="K181" s="9" t="inlineStr">
@@ -18756,7 +18762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q50"/>
+  <dimension ref="A1:Q52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -21243,7 +21249,7 @@
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="H31" s="10" t="inlineStr">
@@ -21253,7 +21259,7 @@
       </c>
       <c r="I31" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="J31" s="9" t="inlineStr">
@@ -21557,6 +21563,16 @@
           <t>07:00-15:30</t>
         </is>
       </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="20" t="n"/>
+      <c r="B35" s="20" t="n"/>
+      <c r="C35" s="20" t="n"/>
+      <c r="D35" s="20" t="n"/>
+      <c r="E35" s="20" t="n"/>
+      <c r="F35" s="20" t="n"/>
+      <c r="G35" s="20" t="n"/>
+      <c r="H35" s="20" t="n"/>
     </row>
     <row r="36" ht="28" customHeight="1">
       <c r="A36" s="17" t="inlineStr">
@@ -21615,114 +21631,114 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="n">
+      <c r="A38" s="21" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="B38" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="C38" s="9" t="n">
+      <c r="C38" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="D38" s="9" t="n">
+      <c r="D38" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="E38" s="9" t="n">
+      <c r="E38" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="F38" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="G38" s="9" t="n">
+      <c r="G38" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="H38" s="9" t="n">
+      <c r="H38" s="21" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="n">
+      <c r="A39" s="21" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="B39" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="C39" s="9" t="n">
+      <c r="C39" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="D39" s="9" t="n">
+      <c r="D39" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="E39" s="9" t="n">
+      <c r="E39" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="F39" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G39" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H39" s="21" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="21" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="B40" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="C40" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="D40" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="E40" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="F40" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="G40" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H40" s="21" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="21" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="B41" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="F39" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="G39" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H39" s="9" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="B40" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="C40" s="9" t="n">
+      <c r="C41" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="D40" s="9" t="n">
+      <c r="D41" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="E40" s="9" t="n">
+      <c r="E41" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="F40" s="9" t="n">
+      <c r="F41" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="G40" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H40" s="9" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="B41" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="C41" s="9" t="n">
+      <c r="G41" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="D41" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="E41" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="F41" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G41" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H41" s="9" t="n">
+      <c r="H41" s="21" t="n">
         <v>4</v>
       </c>
     </row>
@@ -21742,17 +21758,27 @@
         <v>23</v>
       </c>
       <c r="E42" s="19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F42" s="19" t="n">
         <v>24</v>
       </c>
       <c r="G42" s="19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H42" s="19" t="n">
         <v>11</v>
       </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="20" t="n"/>
+      <c r="B43" s="20" t="n"/>
+      <c r="C43" s="20" t="n"/>
+      <c r="D43" s="20" t="n"/>
+      <c r="E43" s="20" t="n"/>
+      <c r="F43" s="20" t="n"/>
+      <c r="G43" s="20" t="n"/>
+      <c r="H43" s="20" t="n"/>
     </row>
     <row r="44" ht="28" customHeight="1">
       <c r="A44" s="17" t="inlineStr">
@@ -21811,114 +21837,114 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="B46" s="9" t="n">
+      <c r="A46" s="21" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="B46" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="C46" s="9" t="n">
+      <c r="C46" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="D46" s="9" t="n">
+      <c r="D46" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="E46" s="9" t="n">
+      <c r="E46" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="F46" s="9" t="n">
+      <c r="F46" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="G46" s="9" t="n">
+      <c r="G46" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="H46" s="9" t="n">
+      <c r="H46" s="21" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="B47" s="9" t="n">
+      <c r="A47" s="21" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="B47" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="C47" s="9" t="n">
+      <c r="C47" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="D47" s="9" t="n">
+      <c r="D47" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="E47" s="9" t="n">
+      <c r="E47" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="F47" s="9" t="n">
+      <c r="F47" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="G47" s="9" t="n">
+      <c r="G47" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="H47" s="9" t="n">
+      <c r="H47" s="21" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="B48" s="9" t="n">
+      <c r="A48" s="21" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="B48" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="C48" s="9" t="n">
+      <c r="C48" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="D48" s="9" t="n">
+      <c r="D48" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="E48" s="9" t="n">
+      <c r="E48" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="F48" s="9" t="n">
+      <c r="F48" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="G48" s="9" t="n">
+      <c r="G48" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="H48" s="9" t="n">
+      <c r="H48" s="21" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="B49" s="9" t="n">
+      <c r="A49" s="21" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="B49" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="C49" s="9" t="n">
+      <c r="C49" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="D49" s="9" t="n">
+      <c r="D49" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="E49" s="9" t="n">
+      <c r="E49" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="F49" s="9" t="n">
+      <c r="F49" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="G49" s="9" t="n">
+      <c r="G49" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="H49" s="9" t="n">
+      <c r="H49" s="21" t="n">
         <v>4</v>
       </c>
     </row>
@@ -21949,12 +21975,32 @@
       <c r="H50" s="19" t="n">
         <v>13</v>
       </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="20" t="n"/>
+      <c r="B51" s="20" t="n"/>
+      <c r="C51" s="20" t="n"/>
+      <c r="D51" s="20" t="n"/>
+      <c r="E51" s="20" t="n"/>
+      <c r="F51" s="20" t="n"/>
+      <c r="G51" s="20" t="n"/>
+      <c r="H51" s="20" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="20" t="n"/>
+      <c r="B52" s="20" t="n"/>
+      <c r="C52" s="20" t="n"/>
+      <c r="D52" s="20" t="n"/>
+      <c r="E52" s="20" t="n"/>
+      <c r="F52" s="20" t="n"/>
+      <c r="G52" s="20" t="n"/>
+      <c r="H52" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A36:H36"/>
+    <mergeCell ref="D2:J2"/>
     <mergeCell ref="A44:H44"/>
-    <mergeCell ref="D2:J2"/>
     <mergeCell ref="K2:Q2"/>
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
@@ -21968,7 +22014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q34"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -22808,17 +22854,17 @@
       </c>
       <c r="L11" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="M11" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="N11" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="O11" s="10" t="inlineStr">
@@ -22833,7 +22879,7 @@
       </c>
       <c r="Q11" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>LEAVE</t>
         </is>
       </c>
     </row>
@@ -23445,6 +23491,16 @@
           <t>08:00-16:30</t>
         </is>
       </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="20" t="n"/>
+      <c r="B19" s="20" t="n"/>
+      <c r="C19" s="20" t="n"/>
+      <c r="D19" s="20" t="n"/>
+      <c r="E19" s="20" t="n"/>
+      <c r="F19" s="20" t="n"/>
+      <c r="G19" s="20" t="n"/>
+      <c r="H19" s="20" t="n"/>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="17" t="inlineStr">
@@ -23503,114 +23559,114 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="n">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="9" t="n">
+      <c r="C22" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="9" t="n">
+      <c r="D22" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="F22" s="9" t="n">
+      <c r="F22" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="G22" s="9" t="n">
+      <c r="G22" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="H22" s="9" t="n">
+      <c r="H22" s="21" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="n">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="C23" s="9" t="n">
+      <c r="C23" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n">
+      <c r="D23" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E23" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="F23" s="9" t="n">
+      <c r="F23" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="G23" s="9" t="n">
+      <c r="G23" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="H23" s="9" t="n">
+      <c r="H23" s="21" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="n">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="C24" s="9" t="n">
+      <c r="C24" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D24" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F24" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="G24" s="9" t="n">
+      <c r="G24" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="H24" s="9" t="n">
+      <c r="H24" s="21" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="n">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="C25" s="9" t="n">
+      <c r="C25" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="D25" s="9" t="n">
+      <c r="D25" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="F25" s="9" t="n">
+      <c r="F25" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="G25" s="9" t="n">
+      <c r="G25" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="H25" s="9" t="n">
+      <c r="H25" s="21" t="n">
         <v>4</v>
       </c>
     </row>
@@ -23641,6 +23697,16 @@
       <c r="H26" s="19" t="n">
         <v>11</v>
       </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="20" t="n"/>
+      <c r="B27" s="20" t="n"/>
+      <c r="C27" s="20" t="n"/>
+      <c r="D27" s="20" t="n"/>
+      <c r="E27" s="20" t="n"/>
+      <c r="F27" s="20" t="n"/>
+      <c r="G27" s="20" t="n"/>
+      <c r="H27" s="20" t="n"/>
     </row>
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="17" t="inlineStr">
@@ -23699,115 +23765,115 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>07:00-15:30</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="n">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>07:00-15:30</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="9" t="n">
+      <c r="C30" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="9" t="n">
+      <c r="D30" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E30" s="9" t="n">
+      <c r="E30" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="F30" s="9" t="n">
+      <c r="F30" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="G30" s="9" t="n">
+      <c r="G30" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="H30" s="9" t="n">
+      <c r="H30" s="21" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>08:00-16:30</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="n">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>08:00-16:30</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="C31" s="9" t="n">
+      <c r="C31" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="9" t="n">
+      <c r="D31" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="E31" s="9" t="n">
+      <c r="E31" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F31" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="G31" s="9" t="n">
+      <c r="G31" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="H31" s="9" t="n">
+      <c r="H31" s="21" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>11:30-20:00</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="n">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>11:30-20:00</t>
+        </is>
+      </c>
+      <c r="B32" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="C32" s="9" t="n">
+      <c r="C32" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="D32" s="9" t="n">
+      <c r="D32" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="E32" s="9" t="n">
+      <c r="E32" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="F32" s="9" t="n">
+      <c r="F32" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="G32" s="9" t="n">
+      <c r="G32" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H32" s="9" t="n">
+      <c r="H32" s="21" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>13:30-22:00</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="n">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>13:30-22:00</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="C33" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="D33" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E33" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="F33" s="9" t="n">
+      <c r="C33" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="G33" s="9" t="n">
+      <c r="D33" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="H33" s="9" t="n">
+      <c r="E33" s="21" t="n">
         <v>3</v>
+      </c>
+      <c r="F33" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G33" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H33" s="21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -23820,13 +23886,13 @@
         <v>11</v>
       </c>
       <c r="C34" s="19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D34" s="19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E34" s="19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F34" s="19" t="n">
         <v>10</v>
@@ -23835,8 +23901,28 @@
         <v>9</v>
       </c>
       <c r="H34" s="19" t="n">
-        <v>10</v>
-      </c>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="20" t="n"/>
+      <c r="B35" s="20" t="n"/>
+      <c r="C35" s="20" t="n"/>
+      <c r="D35" s="20" t="n"/>
+      <c r="E35" s="20" t="n"/>
+      <c r="F35" s="20" t="n"/>
+      <c r="G35" s="20" t="n"/>
+      <c r="H35" s="20" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="20" t="n"/>
+      <c r="B36" s="20" t="n"/>
+      <c r="C36" s="20" t="n"/>
+      <c r="D36" s="20" t="n"/>
+      <c r="E36" s="20" t="n"/>
+      <c r="F36" s="20" t="n"/>
+      <c r="G36" s="20" t="n"/>
+      <c r="H36" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/2026-09-28/Roster_Sep28_Oct11_Full.xlsx
+++ b/2026-09-28/Roster_Sep28_Oct11_Full.xlsx
@@ -1407,27 +1407,27 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
@@ -1442,27 +1442,27 @@
       </c>
       <c r="K11" s="10" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="L11" s="10" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="M11" s="10" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="N11" s="10" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="O11" s="10" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="P11" s="10" t="inlineStr">
@@ -21580,13 +21580,13 @@
           <t>KM Rostered — Week 1 (28 Sep – 4 Oct) - 30 Agents</t>
         </is>
       </c>
-      <c r="B36" s="2" t="n"/>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n"/>
-      <c r="E36" s="2" t="n"/>
-      <c r="F36" s="2" t="n"/>
-      <c r="G36" s="2" t="n"/>
-      <c r="H36" s="2" t="n"/>
+      <c r="B36" s="15" t="n"/>
+      <c r="C36" s="15" t="n"/>
+      <c r="D36" s="15" t="n"/>
+      <c r="E36" s="15" t="n"/>
+      <c r="F36" s="15" t="n"/>
+      <c r="G36" s="15" t="n"/>
+      <c r="H36" s="16" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="18" t="inlineStr">
@@ -21786,13 +21786,13 @@
           <t>KM Rostered — Week 2 (5 Oct – 11 Oct) - 30 Agents</t>
         </is>
       </c>
-      <c r="B44" s="2" t="n"/>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n"/>
-      <c r="E44" s="2" t="n"/>
-      <c r="F44" s="2" t="n"/>
-      <c r="G44" s="2" t="n"/>
-      <c r="H44" s="2" t="n"/>
+      <c r="B44" s="15" t="n"/>
+      <c r="C44" s="15" t="n"/>
+      <c r="D44" s="15" t="n"/>
+      <c r="E44" s="15" t="n"/>
+      <c r="F44" s="15" t="n"/>
+      <c r="G44" s="15" t="n"/>
+      <c r="H44" s="16" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="18" t="inlineStr">
@@ -21999,8 +21999,8 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A44:H44"/>
     <mergeCell ref="D2:J2"/>
-    <mergeCell ref="A44:H44"/>
     <mergeCell ref="K2:Q2"/>
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
@@ -23508,13 +23508,13 @@
           <t>Mirkl Rostered — Week 1 (28 Sep – 4 Oct) - 15 Agents</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="n"/>
-      <c r="G20" s="2" t="n"/>
-      <c r="H20" s="2" t="n"/>
+      <c r="B20" s="15" t="n"/>
+      <c r="C20" s="15" t="n"/>
+      <c r="D20" s="15" t="n"/>
+      <c r="E20" s="15" t="n"/>
+      <c r="F20" s="15" t="n"/>
+      <c r="G20" s="15" t="n"/>
+      <c r="H20" s="16" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="18" t="inlineStr">
@@ -23714,13 +23714,13 @@
           <t>Mirkl Rostered — Week 2 (5 Oct – 11 Oct) - 15 Agents</t>
         </is>
       </c>
-      <c r="B28" s="2" t="n"/>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n"/>
-      <c r="E28" s="2" t="n"/>
-      <c r="F28" s="2" t="n"/>
-      <c r="G28" s="2" t="n"/>
-      <c r="H28" s="2" t="n"/>
+      <c r="B28" s="15" t="n"/>
+      <c r="C28" s="15" t="n"/>
+      <c r="D28" s="15" t="n"/>
+      <c r="E28" s="15" t="n"/>
+      <c r="F28" s="15" t="n"/>
+      <c r="G28" s="15" t="n"/>
+      <c r="H28" s="16" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="18" t="inlineStr">

--- a/2026-09-28/Roster_Sep28_Oct11_Full.xlsx
+++ b/2026-09-28/Roster_Sep28_Oct11_Full.xlsx
@@ -21249,12 +21249,12 @@
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">

--- a/2026-09-28/Roster_Sep28_Oct11_Full.xlsx
+++ b/2026-09-28/Roster_Sep28_Oct11_Full.xlsx
@@ -7033,22 +7033,22 @@
       </c>
       <c r="N79" s="9" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="O79" s="9" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="P79" s="10" t="inlineStr">
         <is>
-          <t>LEAVE</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="Q79" s="10" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>WO</t>
         </is>
       </c>
     </row>
@@ -8975,12 +8975,12 @@
       </c>
       <c r="L103" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="M103" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="N103" s="10" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="O103" s="10" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="P103" s="10" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="Q103" s="9" t="inlineStr">
@@ -9037,22 +9037,22 @@
       </c>
       <c r="G104" s="9" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="H104" s="9" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="I104" s="10" t="inlineStr">
         <is>
-          <t>LEAVE</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="J104" s="10" t="inlineStr">
         <is>
-          <t>LEAVE</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="K104" s="9" t="inlineStr">
@@ -15363,22 +15363,22 @@
       </c>
       <c r="N181" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="O181" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="P181" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="Q181" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>WO</t>
         </is>
       </c>
     </row>
@@ -18762,7 +18762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q52"/>
+  <dimension ref="A1:Q54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -19950,22 +19950,22 @@
       </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="M15" s="10" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="N15" s="9" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="O15" s="12" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="P15" s="9" t="inlineStr">
@@ -20226,7 +20226,7 @@
       </c>
       <c r="O18" s="12" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="P18" s="10" t="inlineStr">
@@ -20236,7 +20236,7 @@
       </c>
       <c r="Q18" s="10" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>WO</t>
         </is>
       </c>
     </row>
@@ -20414,22 +20414,22 @@
       </c>
       <c r="N21" s="12" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="O21" s="12" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="P21" s="10" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="Q21" s="10" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>WO</t>
         </is>
       </c>
     </row>
@@ -21580,13 +21580,13 @@
           <t>KM Rostered — Week 1 (28 Sep – 4 Oct) - 30 Agents</t>
         </is>
       </c>
-      <c r="B36" s="15" t="n"/>
-      <c r="C36" s="15" t="n"/>
-      <c r="D36" s="15" t="n"/>
-      <c r="E36" s="15" t="n"/>
-      <c r="F36" s="15" t="n"/>
-      <c r="G36" s="15" t="n"/>
-      <c r="H36" s="16" t="n"/>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="n"/>
+      <c r="F36" s="2" t="n"/>
+      <c r="G36" s="2" t="n"/>
+      <c r="H36" s="2" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="18" t="inlineStr">
@@ -21677,7 +21677,7 @@
         <v>4</v>
       </c>
       <c r="F39" s="21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G39" s="21" t="n">
         <v>3</v>
@@ -21761,7 +21761,7 @@
         <v>27</v>
       </c>
       <c r="F42" s="19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G42" s="19" t="n">
         <v>16</v>
@@ -21786,13 +21786,13 @@
           <t>KM Rostered — Week 2 (5 Oct – 11 Oct) - 30 Agents</t>
         </is>
       </c>
-      <c r="B44" s="15" t="n"/>
-      <c r="C44" s="15" t="n"/>
-      <c r="D44" s="15" t="n"/>
-      <c r="E44" s="15" t="n"/>
-      <c r="F44" s="15" t="n"/>
-      <c r="G44" s="15" t="n"/>
-      <c r="H44" s="16" t="n"/>
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n"/>
+      <c r="E44" s="2" t="n"/>
+      <c r="F44" s="2" t="n"/>
+      <c r="G44" s="2" t="n"/>
+      <c r="H44" s="2" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="18" t="inlineStr">
@@ -21858,10 +21858,10 @@
         <v>6</v>
       </c>
       <c r="G46" s="21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H46" s="21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
@@ -21902,13 +21902,13 @@
         <v>6</v>
       </c>
       <c r="C48" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="D48" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="E48" s="21" t="n">
         <v>8</v>
-      </c>
-      <c r="D48" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="E48" s="21" t="n">
-        <v>7</v>
       </c>
       <c r="F48" s="21" t="n">
         <v>5</v>
@@ -21917,7 +21917,7 @@
         <v>3</v>
       </c>
       <c r="H48" s="21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -21958,22 +21958,22 @@
         <v>22</v>
       </c>
       <c r="C50" s="19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D50" s="19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E50" s="19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F50" s="19" t="n">
         <v>21</v>
       </c>
       <c r="G50" s="19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H50" s="19" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="51">
@@ -21996,11 +21996,31 @@
       <c r="G52" s="20" t="n"/>
       <c r="H52" s="20" t="n"/>
     </row>
+    <row r="53">
+      <c r="A53" s="20" t="n"/>
+      <c r="B53" s="20" t="n"/>
+      <c r="C53" s="20" t="n"/>
+      <c r="D53" s="20" t="n"/>
+      <c r="E53" s="20" t="n"/>
+      <c r="F53" s="20" t="n"/>
+      <c r="G53" s="20" t="n"/>
+      <c r="H53" s="20" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="20" t="n"/>
+      <c r="B54" s="20" t="n"/>
+      <c r="C54" s="20" t="n"/>
+      <c r="D54" s="20" t="n"/>
+      <c r="E54" s="20" t="n"/>
+      <c r="F54" s="20" t="n"/>
+      <c r="G54" s="20" t="n"/>
+      <c r="H54" s="20" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A36:H36"/>
+    <mergeCell ref="D2:J2"/>
     <mergeCell ref="A44:H44"/>
-    <mergeCell ref="D2:J2"/>
     <mergeCell ref="K2:Q2"/>
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
@@ -22014,7 +22034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q36"/>
+  <dimension ref="A1:Q38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -22240,17 +22260,17 @@
       </c>
       <c r="K4" s="10" t="inlineStr">
         <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="M4" s="9" t="inlineStr">
+        <is>
           <t>LEAVE</t>
-        </is>
-      </c>
-      <c r="L4" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="M4" s="9" t="inlineStr">
-        <is>
-          <t>WO</t>
         </is>
       </c>
       <c r="N4" s="9" t="inlineStr">
@@ -22389,12 +22409,12 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
@@ -22404,12 +22424,12 @@
       </c>
       <c r="I6" s="10" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="J6" s="10" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -23508,13 +23528,13 @@
           <t>Mirkl Rostered — Week 1 (28 Sep – 4 Oct) - 15 Agents</t>
         </is>
       </c>
-      <c r="B20" s="15" t="n"/>
-      <c r="C20" s="15" t="n"/>
-      <c r="D20" s="15" t="n"/>
-      <c r="E20" s="15" t="n"/>
-      <c r="F20" s="15" t="n"/>
-      <c r="G20" s="15" t="n"/>
-      <c r="H20" s="16" t="n"/>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="18" t="inlineStr">
@@ -23664,10 +23684,10 @@
         <v>3</v>
       </c>
       <c r="G25" s="21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H25" s="21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -23692,10 +23712,10 @@
         <v>11</v>
       </c>
       <c r="G26" s="19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H26" s="19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
@@ -23714,13 +23734,13 @@
           <t>Mirkl Rostered — Week 2 (5 Oct – 11 Oct) - 15 Agents</t>
         </is>
       </c>
-      <c r="B28" s="15" t="n"/>
-      <c r="C28" s="15" t="n"/>
-      <c r="D28" s="15" t="n"/>
-      <c r="E28" s="15" t="n"/>
-      <c r="F28" s="15" t="n"/>
-      <c r="G28" s="15" t="n"/>
-      <c r="H28" s="16" t="n"/>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+      <c r="E28" s="2" t="n"/>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="2" t="n"/>
+      <c r="H28" s="2" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="18" t="inlineStr">
@@ -23923,6 +23943,26 @@
       <c r="F36" s="20" t="n"/>
       <c r="G36" s="20" t="n"/>
       <c r="H36" s="20" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="20" t="n"/>
+      <c r="B37" s="20" t="n"/>
+      <c r="C37" s="20" t="n"/>
+      <c r="D37" s="20" t="n"/>
+      <c r="E37" s="20" t="n"/>
+      <c r="F37" s="20" t="n"/>
+      <c r="G37" s="20" t="n"/>
+      <c r="H37" s="20" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="20" t="n"/>
+      <c r="B38" s="20" t="n"/>
+      <c r="C38" s="20" t="n"/>
+      <c r="D38" s="20" t="n"/>
+      <c r="E38" s="20" t="n"/>
+      <c r="F38" s="20" t="n"/>
+      <c r="G38" s="20" t="n"/>
+      <c r="H38" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/2026-09-28/Roster_Sep28_Oct11_Full.xlsx
+++ b/2026-09-28/Roster_Sep28_Oct11_Full.xlsx
@@ -8975,12 +8975,12 @@
       </c>
       <c r="L103" s="10" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="M103" s="10" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="N103" s="10" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="O103" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="P103" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="Q103" s="9" t="inlineStr">
@@ -9037,22 +9037,22 @@
       </c>
       <c r="G104" s="9" t="inlineStr">
         <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="H104" s="9" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="I104" s="10" t="inlineStr">
+        <is>
           <t>LEAVE</t>
         </is>
       </c>
-      <c r="H104" s="9" t="inlineStr">
+      <c r="J104" s="10" t="inlineStr">
         <is>
           <t>LEAVE</t>
-        </is>
-      </c>
-      <c r="I104" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="J104" s="10" t="inlineStr">
-        <is>
-          <t>WO</t>
         </is>
       </c>
       <c r="K104" s="9" t="inlineStr">
@@ -18762,7 +18762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q54"/>
+  <dimension ref="A1:Q56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -19950,22 +19950,22 @@
       </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="M15" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="N15" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="O15" s="12" t="inlineStr">
         <is>
-          <t>LEAVE</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="P15" s="9" t="inlineStr">
@@ -20226,7 +20226,7 @@
       </c>
       <c r="O18" s="12" t="inlineStr">
         <is>
-          <t>LEAVE</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="P18" s="10" t="inlineStr">
@@ -20236,7 +20236,7 @@
       </c>
       <c r="Q18" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
     </row>
@@ -20414,22 +20414,22 @@
       </c>
       <c r="N21" s="12" t="inlineStr">
         <is>
-          <t>LEAVE</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="O21" s="12" t="inlineStr">
         <is>
-          <t>LEAVE</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="P21" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="Q21" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
     </row>
@@ -21858,10 +21858,10 @@
         <v>6</v>
       </c>
       <c r="G46" s="21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H46" s="21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
@@ -21902,13 +21902,13 @@
         <v>6</v>
       </c>
       <c r="C48" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="D48" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E48" s="21" t="n">
         <v>7</v>
-      </c>
-      <c r="D48" s="21" t="n">
-        <v>7</v>
-      </c>
-      <c r="E48" s="21" t="n">
-        <v>8</v>
       </c>
       <c r="F48" s="21" t="n">
         <v>5</v>
@@ -21917,7 +21917,7 @@
         <v>3</v>
       </c>
       <c r="H48" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -21958,22 +21958,22 @@
         <v>22</v>
       </c>
       <c r="C50" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="D50" s="19" t="n">
         <v>23</v>
       </c>
-      <c r="D50" s="19" t="n">
-        <v>22</v>
-      </c>
       <c r="E50" s="19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F50" s="19" t="n">
         <v>21</v>
       </c>
       <c r="G50" s="19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H50" s="19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="51">
@@ -22015,6 +22015,26 @@
       <c r="F54" s="20" t="n"/>
       <c r="G54" s="20" t="n"/>
       <c r="H54" s="20" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="20" t="n"/>
+      <c r="B55" s="20" t="n"/>
+      <c r="C55" s="20" t="n"/>
+      <c r="D55" s="20" t="n"/>
+      <c r="E55" s="20" t="n"/>
+      <c r="F55" s="20" t="n"/>
+      <c r="G55" s="20" t="n"/>
+      <c r="H55" s="20" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="20" t="n"/>
+      <c r="B56" s="20" t="n"/>
+      <c r="C56" s="20" t="n"/>
+      <c r="D56" s="20" t="n"/>
+      <c r="E56" s="20" t="n"/>
+      <c r="F56" s="20" t="n"/>
+      <c r="G56" s="20" t="n"/>
+      <c r="H56" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -22034,7 +22054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q38"/>
+  <dimension ref="A1:Q40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -22260,7 +22280,7 @@
       </c>
       <c r="K4" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="L4" s="10" t="inlineStr">
@@ -22270,7 +22290,7 @@
       </c>
       <c r="M4" s="9" t="inlineStr">
         <is>
-          <t>LEAVE</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="N4" s="9" t="inlineStr">
@@ -22409,12 +22429,12 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>LEAVE</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>LEAVE</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
@@ -22424,12 +22444,12 @@
       </c>
       <c r="I6" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="J6" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -23684,10 +23704,10 @@
         <v>3</v>
       </c>
       <c r="G25" s="21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H25" s="21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -23712,10 +23732,10 @@
         <v>11</v>
       </c>
       <c r="G26" s="19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H26" s="19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27">
@@ -23963,6 +23983,26 @@
       <c r="F38" s="20" t="n"/>
       <c r="G38" s="20" t="n"/>
       <c r="H38" s="20" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="20" t="n"/>
+      <c r="B39" s="20" t="n"/>
+      <c r="C39" s="20" t="n"/>
+      <c r="D39" s="20" t="n"/>
+      <c r="E39" s="20" t="n"/>
+      <c r="F39" s="20" t="n"/>
+      <c r="G39" s="20" t="n"/>
+      <c r="H39" s="20" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="20" t="n"/>
+      <c r="B40" s="20" t="n"/>
+      <c r="C40" s="20" t="n"/>
+      <c r="D40" s="20" t="n"/>
+      <c r="E40" s="20" t="n"/>
+      <c r="F40" s="20" t="n"/>
+      <c r="G40" s="20" t="n"/>
+      <c r="H40" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/2026-09-28/Roster_Sep28_Oct11_Full.xlsx
+++ b/2026-09-28/Roster_Sep28_Oct11_Full.xlsx
@@ -8786,12 +8786,12 @@
       </c>
       <c r="I101" s="9" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="J101" s="9" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="K101" s="9" t="inlineStr">
@@ -15338,12 +15338,12 @@
       </c>
       <c r="I181" s="9" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="J181" s="9" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="K181" s="9" t="inlineStr">
@@ -18762,7 +18762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q56"/>
+  <dimension ref="A1:Q58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -22036,6 +22036,26 @@
       <c r="G56" s="20" t="n"/>
       <c r="H56" s="20" t="n"/>
     </row>
+    <row r="57">
+      <c r="A57" s="20" t="n"/>
+      <c r="B57" s="20" t="n"/>
+      <c r="C57" s="20" t="n"/>
+      <c r="D57" s="20" t="n"/>
+      <c r="E57" s="20" t="n"/>
+      <c r="F57" s="20" t="n"/>
+      <c r="G57" s="20" t="n"/>
+      <c r="H57" s="20" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="20" t="n"/>
+      <c r="B58" s="20" t="n"/>
+      <c r="C58" s="20" t="n"/>
+      <c r="D58" s="20" t="n"/>
+      <c r="E58" s="20" t="n"/>
+      <c r="F58" s="20" t="n"/>
+      <c r="G58" s="20" t="n"/>
+      <c r="H58" s="20" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A36:H36"/>
@@ -22054,7 +22074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q40"/>
+  <dimension ref="A1:Q42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -24004,6 +24024,26 @@
       <c r="G40" s="20" t="n"/>
       <c r="H40" s="20" t="n"/>
     </row>
+    <row r="41">
+      <c r="A41" s="20" t="n"/>
+      <c r="B41" s="20" t="n"/>
+      <c r="C41" s="20" t="n"/>
+      <c r="D41" s="20" t="n"/>
+      <c r="E41" s="20" t="n"/>
+      <c r="F41" s="20" t="n"/>
+      <c r="G41" s="20" t="n"/>
+      <c r="H41" s="20" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="20" t="n"/>
+      <c r="B42" s="20" t="n"/>
+      <c r="C42" s="20" t="n"/>
+      <c r="D42" s="20" t="n"/>
+      <c r="E42" s="20" t="n"/>
+      <c r="F42" s="20" t="n"/>
+      <c r="G42" s="20" t="n"/>
+      <c r="H42" s="20" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A20:H20"/>

--- a/2026-09-28/Roster_Sep28_Oct11_Full.xlsx
+++ b/2026-09-28/Roster_Sep28_Oct11_Full.xlsx
@@ -21580,13 +21580,13 @@
           <t>KM Rostered — Week 1 (28 Sep – 4 Oct) - 30 Agents</t>
         </is>
       </c>
-      <c r="B36" s="2" t="n"/>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n"/>
-      <c r="E36" s="2" t="n"/>
-      <c r="F36" s="2" t="n"/>
-      <c r="G36" s="2" t="n"/>
-      <c r="H36" s="2" t="n"/>
+      <c r="B36" s="15" t="n"/>
+      <c r="C36" s="15" t="n"/>
+      <c r="D36" s="15" t="n"/>
+      <c r="E36" s="15" t="n"/>
+      <c r="F36" s="15" t="n"/>
+      <c r="G36" s="15" t="n"/>
+      <c r="H36" s="16" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="18" t="inlineStr">
@@ -21786,13 +21786,13 @@
           <t>KM Rostered — Week 2 (5 Oct – 11 Oct) - 30 Agents</t>
         </is>
       </c>
-      <c r="B44" s="2" t="n"/>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n"/>
-      <c r="E44" s="2" t="n"/>
-      <c r="F44" s="2" t="n"/>
-      <c r="G44" s="2" t="n"/>
-      <c r="H44" s="2" t="n"/>
+      <c r="B44" s="15" t="n"/>
+      <c r="C44" s="15" t="n"/>
+      <c r="D44" s="15" t="n"/>
+      <c r="E44" s="15" t="n"/>
+      <c r="F44" s="15" t="n"/>
+      <c r="G44" s="15" t="n"/>
+      <c r="H44" s="16" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="18" t="inlineStr">
@@ -22059,8 +22059,8 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A44:H44"/>
     <mergeCell ref="D2:J2"/>
-    <mergeCell ref="A44:H44"/>
     <mergeCell ref="K2:Q2"/>
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
@@ -22362,7 +22362,7 @@
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>07:00-15:30</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
@@ -22444,22 +22444,22 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>LEAVE</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
@@ -22633,7 +22633,7 @@
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr">
@@ -22643,17 +22643,17 @@
       </c>
       <c r="J8" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="K8" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="M8" s="9" t="inlineStr">
@@ -22678,7 +22678,7 @@
       </c>
       <c r="Q8" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
     </row>
@@ -23048,7 +23048,7 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -23068,22 +23068,22 @@
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="J13" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="K13" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="L13" s="9" t="inlineStr">
@@ -23103,17 +23103,17 @@
       </c>
       <c r="O13" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="P13" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="Q13" s="9" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>WO</t>
         </is>
       </c>
     </row>
@@ -23314,12 +23314,12 @@
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
@@ -23329,12 +23329,12 @@
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="J16" s="9" t="inlineStr">
@@ -23349,12 +23349,12 @@
       </c>
       <c r="L16" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="M16" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>08:00-16:30</t>
         </is>
       </c>
       <c r="N16" s="9" t="inlineStr">
@@ -23364,12 +23364,12 @@
       </c>
       <c r="O16" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="P16" s="9" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="Q16" s="9" t="inlineStr">
@@ -23568,13 +23568,13 @@
           <t>Mirkl Rostered — Week 1 (28 Sep – 4 Oct) - 15 Agents</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="n"/>
-      <c r="G20" s="2" t="n"/>
-      <c r="H20" s="2" t="n"/>
+      <c r="B20" s="15" t="n"/>
+      <c r="C20" s="15" t="n"/>
+      <c r="D20" s="15" t="n"/>
+      <c r="E20" s="15" t="n"/>
+      <c r="F20" s="15" t="n"/>
+      <c r="G20" s="15" t="n"/>
+      <c r="H20" s="16" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="18" t="inlineStr">
@@ -23774,13 +23774,13 @@
           <t>Mirkl Rostered — Week 2 (5 Oct – 11 Oct) - 15 Agents</t>
         </is>
       </c>
-      <c r="B28" s="2" t="n"/>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n"/>
-      <c r="E28" s="2" t="n"/>
-      <c r="F28" s="2" t="n"/>
-      <c r="G28" s="2" t="n"/>
-      <c r="H28" s="2" t="n"/>
+      <c r="B28" s="15" t="n"/>
+      <c r="C28" s="15" t="n"/>
+      <c r="D28" s="15" t="n"/>
+      <c r="E28" s="15" t="n"/>
+      <c r="F28" s="15" t="n"/>
+      <c r="G28" s="15" t="n"/>
+      <c r="H28" s="16" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="18" t="inlineStr">

--- a/2026-09-28/Roster_Sep28_Oct11_Full.xlsx
+++ b/2026-09-28/Roster_Sep28_Oct11_Full.xlsx
@@ -15328,12 +15328,12 @@
       </c>
       <c r="G181" s="10" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="H181" s="10" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="I181" s="9" t="inlineStr">
@@ -21254,12 +21254,12 @@
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">
         <is>
-          <t>08:00-16:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="J31" s="9" t="inlineStr">

--- a/2026-09-28/Roster_Sep28_Oct11_Full.xlsx
+++ b/2026-09-28/Roster_Sep28_Oct11_Full.xlsx
@@ -22362,7 +22362,7 @@
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
-          <t>07:00-15:30</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
@@ -22633,7 +22633,7 @@
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr">
@@ -22643,17 +22643,17 @@
       </c>
       <c r="J8" s="10" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="K8" s="10" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>11:30-20:00</t>
         </is>
       </c>
       <c r="M8" s="9" t="inlineStr">
@@ -22678,7 +22678,7 @@
       </c>
       <c r="Q8" s="10" t="inlineStr">
         <is>
-          <t>11:30-20:00</t>
+          <t>WO</t>
         </is>
       </c>
     </row>

--- a/2026-09-28/Roster_Sep28_Oct11_Full.xlsx
+++ b/2026-09-28/Roster_Sep28_Oct11_Full.xlsx
@@ -8766,12 +8766,12 @@
       </c>
       <c r="E101" s="10" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="G101" s="9" t="inlineStr">

--- a/2026-09-28/Roster_Sep28_Oct11_Full.xlsx
+++ b/2026-09-28/Roster_Sep28_Oct11_Full.xlsx
@@ -8766,12 +8766,12 @@
       </c>
       <c r="E101" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>13:30-22:00</t>
         </is>
       </c>
       <c r="G101" s="9" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="I101" s="9" t="inlineStr">
         <is>
-          <t>LEAVE</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="J101" s="9" t="inlineStr">
         <is>
-          <t>LEAVE</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="K101" s="9" t="inlineStr">
